--- a/tame_output/ON/bt/strategyON_20240501.xlsx
+++ b/tame_output/ON/bt/strategyON_20240501.xlsx
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.53733184493233</v>
+        <v>-4.537259786903014</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9555434516733265</v>
+        <v>0.9555722748850528</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.8639177910555522</v>
+        <v>-0.8638457330262357</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.252481939326675</v>
+        <v>2.252525174144265</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240501.xlsx
+++ b/tame_output/ON/bt/strategyON_20240501.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.9%</t>
+          <t>-81.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.3%</t>
+          <t>117.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.6%</t>
+          <t>440.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.3%</t>
+          <t>-623.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-67.7%</t>
+          <t>-87.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.7%</t>
+          <t>-284.1%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.9%</t>
+          <t>-36.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-164.1%</t>
+          <t>-166.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-310.4%</t>
+          <t>-309.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-220.8%</t>
+          <t>-220.3%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.386279098421475</v>
+        <v>-7.479365989750649</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.0009581819165447314</v>
+        <v>-0.03819293844821425</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.92639919402671</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.082711609417497</v>
+        <v>-7.17579850074667</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1240679372056954</v>
+        <v>0.0868331806740259</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.92639919402671</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.009231700565483</v>
+        <v>-7.102318591894656</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1667874068010549</v>
+        <v>0.1295526502693853</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.852919285174696</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.78419870089666</v>
+        <v>-6.877285592225833</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2558210842848809</v>
+        <v>0.2185863277532114</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.627886285505873</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.569564323260253</v>
+        <v>-6.662651214589427</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3463696363937609</v>
+        <v>0.3091348798620914</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.413251907869467</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.302963966285901</v>
+        <v>-6.396050857615075</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4342040379672971</v>
+        <v>0.3969692814356276</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.413251907869467</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.062533469481041</v>
+        <v>-6.155620360810214</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5321193133141189</v>
+        <v>0.4948845567824494</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.172821411064606</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.819742661831595</v>
+        <v>-5.912829553160769</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6331649502087173</v>
+        <v>0.5959301936770478</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.172821411064606</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.70380281220641</v>
+        <v>-5.796889703535584</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6802194739761314</v>
+        <v>0.6429847174444618</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.095999680048482</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.461147223783247</v>
+        <v>-5.55423411511242</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.77427978056539</v>
+        <v>0.737045024033721</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.095999680048482</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.241126425746236</v>
+        <v>-5.33421331707541</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8638671367908084</v>
+        <v>0.8266323802591393</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.9547798349805021</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.041877795841427</v>
+        <v>-5.134964687170601</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9594607715545553</v>
+        <v>0.9222260150228863</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.9547798349805021</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.882362692322057</v>
+        <v>-4.975449583651231</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.024412657402605</v>
+        <v>0.9871779008709358</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7952647314611322</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.73769054722232</v>
+        <v>-4.830777438551493</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.09236961800394</v>
+        <v>1.055134861472271</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.6505925863613948</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.797565374580012</v>
+        <v>-4.890652265909186</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.054457178462289</v>
+        <v>1.01722242193062</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.7104674137190869</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.710765876801004</v>
+        <v>-4.803852768130177</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.111577470896459</v>
+        <v>1.074342714364789</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.7104674137190869</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.71323558326281</v>
+        <v>-4.806322474591983</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.110661989685148</v>
+        <v>1.073427233153479</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.7129371201808932</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.78160576958682</v>
+        <v>-4.874692660915994</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.094320837630246</v>
+        <v>1.057086081098577</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.7036614211446782</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.660189339960343</v>
+        <v>-4.753276231289517</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.133324118112728</v>
+        <v>1.096089361581059</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.7036614211446782</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.691182499289049</v>
+        <v>-4.784269390618222</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9456364194216327</v>
+        <v>0.9084016628899634</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.7036614211446782</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.515708239496579</v>
+        <v>-4.608795130825753</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.020393355330408</v>
+        <v>0.983158598798739</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.7036614211446782</v>
@@ -46171,10 +46171,10 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.626644492137828</v>
+        <v>-4.719731383467002</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9760303281607063</v>
+        <v>0.9387955716290368</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.7036614211446782</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.829671069681061</v>
+        <v>-4.922757961010235</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8979510823633186</v>
+        <v>0.8607163258316493</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.9066879986879116</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.671745470745768</v>
+        <v>-4.764832362074942</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9712937083695681</v>
+        <v>0.9340589518378988</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.9066879986879116</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.820066724556897</v>
+        <v>-4.91315361588607</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.906911477418977</v>
+        <v>0.8696767208873075</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.9066879986879116</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.821249809207957</v>
+        <v>-4.914336700537131</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8982140190030783</v>
+        <v>0.860979262471409</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.9123310471544231</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.698122102213874</v>
+        <v>-4.791208993543048</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9480169748338132</v>
+        <v>0.9107822183021437</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.9123310471544231</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.605311620763015</v>
+        <v>-4.698398512092188</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9144138593055227</v>
+        <v>0.8771791027738531</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.8195205657035638</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.556748568541985</v>
+        <v>-4.649835459871158</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9357125561185353</v>
+        <v>0.898477799586866</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.7709575134825336</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.444077350305735</v>
+        <v>-4.537164241634908</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9758567519247585</v>
+        <v>0.938621995393089</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.6582862952462833</v>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.331700349123062</v>
+        <v>-4.424787240452235</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.026298848228495</v>
+        <v>0.9890640916968254</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.6582862952462833</v>
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.840494709743316</v>
+        <v>3.398147983633035</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.537259786903014</v>
+        <v>-4.623021809338966</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9555722748850528</v>
+        <v>0.9212674659106721</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.8638457330262357</v>
+        <v>-0.856520864133014</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.252525174144265</v>
+        <v>2.256920095480198</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240501.xlsx
+++ b/tame_output/ON/bt/strategyON_20240501.xlsx
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>

--- a/tame_output/ON/bt/strategyON_20240501.xlsx
+++ b/tame_output/ON/bt/strategyON_20240501.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-13.9%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.1%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.0%</t>
+          <t>116.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.6%</t>
+          <t>137.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.2%</t>
+          <t>444.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-623.9%</t>
+          <t>-593.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-87.8%</t>
+          <t>-67.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-284.1%</t>
+          <t>-272.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.8%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-166.9%</t>
+          <t>-166.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-309.6%</t>
+          <t>-289.0%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-220.3%</t>
+          <t>-148.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1950"/>
+  <dimension ref="A1:G1951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.479365989750649</v>
+        <v>-7.386279098421475</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.03819293844821425</v>
+        <v>-0.0009581819165447314</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.92639919402671</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.17579850074667</v>
+        <v>-7.082711609417497</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.0868331806740259</v>
+        <v>0.1240679372056954</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.92639919402671</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.102318591894656</v>
+        <v>-7.009231700565483</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1295526502693853</v>
+        <v>0.1667874068010549</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.852919285174696</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.877285592225833</v>
+        <v>-6.78419870089666</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2185863277532114</v>
+        <v>0.2558210842848809</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.627886285505873</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.662651214589427</v>
+        <v>-6.569564323260253</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3091348798620914</v>
+        <v>0.3463696363937609</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.413251907869467</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.396050857615075</v>
+        <v>-6.302963966285901</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3969692814356276</v>
+        <v>0.4342040379672971</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.413251907869467</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.155620360810214</v>
+        <v>-6.062533469481041</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4948845567824494</v>
+        <v>0.5321193133141189</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.172821411064606</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.912829553160769</v>
+        <v>-5.819742661831595</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5959301936770478</v>
+        <v>0.6331649502087173</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.172821411064606</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.796889703535584</v>
+        <v>-5.70380281220641</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6429847174444618</v>
+        <v>0.6802194739761314</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.095999680048482</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.55423411511242</v>
+        <v>-5.461147223783247</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.737045024033721</v>
+        <v>0.77427978056539</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.095999680048482</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.33421331707541</v>
+        <v>-5.241126425746236</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8266323802591393</v>
+        <v>0.8638671367908084</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.9547798349805021</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.134964687170601</v>
+        <v>-5.041877795841427</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9222260150228863</v>
+        <v>0.9594607715545553</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.9547798349805021</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.975449583651231</v>
+        <v>-4.882362692322057</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9871779008709358</v>
+        <v>1.024412657402605</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7952647314611322</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.830777438551493</v>
+        <v>-4.73769054722232</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.055134861472271</v>
+        <v>1.09236961800394</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.6505925863613948</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.890652265909186</v>
+        <v>-4.797565374580012</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.01722242193062</v>
+        <v>1.054457178462289</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.7104674137190869</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.803852768130177</v>
+        <v>-4.710765876801004</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.074342714364789</v>
+        <v>1.111577470896459</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.7104674137190869</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.806322474591983</v>
+        <v>-4.71323558326281</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.073427233153479</v>
+        <v>1.110661989685148</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.7129371201808932</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.874692660915994</v>
+        <v>-4.78160576958682</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.057086081098577</v>
+        <v>1.094320837630246</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.7036614211446782</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.753276231289517</v>
+        <v>-4.660189339960343</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.096089361581059</v>
+        <v>1.133324118112728</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.7036614211446782</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.784269390618222</v>
+        <v>-4.691182499289049</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9084016628899634</v>
+        <v>0.9456364194216327</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.7036614211446782</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.608795130825753</v>
+        <v>-4.515708239496579</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.983158598798739</v>
+        <v>1.020393355330408</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.7036614211446782</v>
@@ -46171,10 +46171,10 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.719731383467002</v>
+        <v>-4.626644492137828</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9387955716290368</v>
+        <v>0.9760303281607063</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.7036614211446782</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.922757961010235</v>
+        <v>-4.829671069681061</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8607163258316493</v>
+        <v>0.8979510823633186</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.9066879986879116</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.764832362074942</v>
+        <v>-4.671745470745768</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9340589518378988</v>
+        <v>0.9712937083695681</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.9066879986879116</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.91315361588607</v>
+        <v>-4.820066724556897</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8696767208873075</v>
+        <v>0.906911477418977</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.9066879986879116</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.914336700537131</v>
+        <v>-4.821249809207957</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.860979262471409</v>
+        <v>0.8982140190030783</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.9123310471544231</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.791208993543048</v>
+        <v>-4.698122102213874</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9107822183021437</v>
+        <v>0.9480169748338132</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.9123310471544231</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.698398512092188</v>
+        <v>-4.605311620763015</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8771791027738531</v>
+        <v>0.9144138593055227</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.8195205657035638</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.649835459871158</v>
+        <v>-4.556748568541985</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.898477799586866</v>
+        <v>0.9357125561185353</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.7709575134825336</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.537164241634908</v>
+        <v>-4.444077350305735</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.938621995393089</v>
+        <v>0.9758567519247585</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.6582862952462833</v>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.424787240452235</v>
+        <v>-4.331700349123062</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9890640916968254</v>
+        <v>1.026298848228495</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.6582862952462833</v>
@@ -46395,22 +46395,45 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.398147983633035</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.623021809338966</v>
+        <v>-4.323281729620129</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9212674659106721</v>
+        <v>1.041163497798207</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.856520864133014</v>
+        <v>-0.6498676757433512</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.256920095480198</v>
+        <v>2.380912008513995</v>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" s="2" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B1951" t="n">
+        <v>3.849015750404747</v>
+      </c>
+      <c r="C1951" t="n">
+        <v>2.977699090470047</v>
+      </c>
+      <c r="D1951" t="n">
+        <v>-4.323281729620129</v>
+      </c>
+      <c r="E1951" t="n">
+        <v>1.041163497798207</v>
+      </c>
+      <c r="F1951" t="n">
+        <v>-0.6498676757433512</v>
+      </c>
+      <c r="G1951" t="n">
+        <v>2.970762887456415</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240501.xlsx
+++ b/tame_output/ON/bt/strategyON_20240501.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>10.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-46.7%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-81.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.0%</t>
+          <t>137.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.6%</t>
+          <t>440.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-593.9%</t>
+          <t>-623.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-67.7%</t>
+          <t>-87.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-272.1%</t>
+          <t>-284.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-36.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-166.6%</t>
+          <t>-166.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-289.0%</t>
+          <t>-309.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-148.9%</t>
+          <t>-181.8%</t>
         </is>
       </c>
     </row>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.386279098421475</v>
+        <v>-7.479365989750649</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.0009581819165447314</v>
+        <v>-0.03819293844821425</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.92639919402671</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.082711609417497</v>
+        <v>-7.17579850074667</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1240679372056954</v>
+        <v>0.0868331806740259</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.92639919402671</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.009231700565483</v>
+        <v>-7.102318591894656</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1667874068010549</v>
+        <v>0.1295526502693853</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.852919285174696</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.78419870089666</v>
+        <v>-6.877285592225833</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2558210842848809</v>
+        <v>0.2185863277532114</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.627886285505873</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.569564323260253</v>
+        <v>-6.662651214589427</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3463696363937609</v>
+        <v>0.3091348798620914</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.413251907869467</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.302963966285901</v>
+        <v>-6.396050857615075</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4342040379672971</v>
+        <v>0.3969692814356276</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.413251907869467</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.062533469481041</v>
+        <v>-6.155620360810214</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5321193133141189</v>
+        <v>0.4948845567824494</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.172821411064606</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.819742661831595</v>
+        <v>-5.912829553160769</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6331649502087173</v>
+        <v>0.5959301936770478</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.172821411064606</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.70380281220641</v>
+        <v>-5.796889703535584</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6802194739761314</v>
+        <v>0.6429847174444618</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.095999680048482</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.461147223783247</v>
+        <v>-5.55423411511242</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.77427978056539</v>
+        <v>0.737045024033721</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.095999680048482</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.241126425746236</v>
+        <v>-5.33421331707541</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8638671367908084</v>
+        <v>0.8266323802591393</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.9547798349805021</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.041877795841427</v>
+        <v>-5.134964687170601</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9594607715545553</v>
+        <v>0.9222260150228863</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.9547798349805021</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.882362692322057</v>
+        <v>-4.975449583651231</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.024412657402605</v>
+        <v>0.9871779008709358</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7952647314611322</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.73769054722232</v>
+        <v>-4.830777438551493</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.09236961800394</v>
+        <v>1.055134861472271</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.6505925863613948</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.797565374580012</v>
+        <v>-4.890652265909186</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.054457178462289</v>
+        <v>1.01722242193062</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.7104674137190869</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.710765876801004</v>
+        <v>-4.803852768130177</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.111577470896459</v>
+        <v>1.074342714364789</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.7104674137190869</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900694</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.71323558326281</v>
+        <v>-4.806322474591983</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.110661989685148</v>
+        <v>1.073427233153479</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.7129371201808932</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473601</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.78160576958682</v>
+        <v>-4.874692660915994</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.094320837630246</v>
+        <v>1.057086081098577</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.7036614211446782</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.660189339960343</v>
+        <v>-4.753276231289517</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.133324118112728</v>
+        <v>1.096089361581059</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.7036614211446782</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.691182499289049</v>
+        <v>-4.784269390618222</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9456364194216327</v>
+        <v>0.9084016628899634</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.7036614211446782</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.515708239496579</v>
+        <v>-4.608795130825753</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.020393355330408</v>
+        <v>0.983158598798739</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.7036614211446782</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.626644492137828</v>
+        <v>-4.719731383467002</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9760303281607063</v>
+        <v>0.9387955716290368</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.7036614211446782</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.829671069681061</v>
+        <v>-4.922757961010235</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8979510823633186</v>
+        <v>0.8607163258316493</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.9066879986879116</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.671745470745768</v>
+        <v>-4.764832362074942</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9712937083695681</v>
+        <v>0.9340589518378988</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.9066879986879116</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212298</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.820066724556897</v>
+        <v>-4.91315361588607</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.906911477418977</v>
+        <v>0.8696767208873075</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.9066879986879116</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786045</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.821249809207957</v>
+        <v>-4.914336700537131</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8982140190030783</v>
+        <v>0.860979262471409</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.9123310471544231</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.698122102213874</v>
+        <v>-4.791208993543048</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9480169748338132</v>
+        <v>0.9107822183021437</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.9123310471544231</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.605311620763015</v>
+        <v>-4.698398512092188</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9144138593055227</v>
+        <v>0.8771791027738531</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.8195205657035638</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.556748568541985</v>
+        <v>-4.649835459871158</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9357125561185353</v>
+        <v>0.898477799586866</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.7709575134825336</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.444077350305735</v>
+        <v>-4.537164241634908</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9758567519247585</v>
+        <v>0.938621995393089</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.6582862952462833</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.331700349123062</v>
+        <v>-4.424787240452235</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.026298848228495</v>
+        <v>0.9890640916968254</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.6582862952462833</v>
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.323281729620129</v>
+        <v>-4.623021809338966</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.041163497798207</v>
+        <v>0.9212674659106721</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.6498676757433512</v>
+        <v>-0.856520864133014</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.380912008513995</v>
+        <v>2.256920095480198</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.849015750404747</v>
+        <v>3.381690605938775</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.977699090470047</v>
+        <v>2.649309575323622</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.323281729620129</v>
+        <v>-4.623021809338966</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.041163497798207</v>
+        <v>0.9212674659106721</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6498676757433512</v>
+        <v>-0.856520864133014</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.970762887456415</v>
+        <v>2.64237337230999</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240501.xlsx
+++ b/tame_output/ON/bt/strategyON_20240501.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-46.7%</t>
+          <t>-30.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.1%</t>
+          <t>-80.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.9%</t>
+          <t>117.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.5%</t>
+          <t>137.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-720.6%</t>
+          <t>-717.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.0%</t>
+          <t>-57.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.0%</t>
+          <t>445.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-623.9%</t>
+          <t>-611.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-288.6%</t>
+          <t>-287.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.4%</t>
+          <t>-45.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-87.7%</t>
+          <t>-63.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-284.1%</t>
+          <t>-279.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.8%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-344.9%</t>
+          <t>-341.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-166.9%</t>
+          <t>-163.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-309.6%</t>
+          <t>-306.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-207.3%</t>
+          <t>-205.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-181.8%</t>
+          <t>-165.9%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.875505373556535</v>
+        <v>-1.844765679408686</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.366361693705503</v>
+        <v>2.378657571364643</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6514310370124661</v>
+        <v>0.682170731160316</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.507778889649344</v>
+        <v>3.526222706138054</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.214663751145058</v>
+        <v>-2.183924056997208</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.223782641976543</v>
+        <v>2.236078519635683</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.312272659423944</v>
+        <v>0.3430123535717939</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.29736816240268</v>
+        <v>3.31581197889139</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.542680972872537</v>
+        <v>-2.511941278724687</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.11291404302432</v>
+        <v>2.12520992068346</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.01574456230353516</v>
+        <v>0.01499513184431478</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.120896119104961</v>
+        <v>3.139339935593671</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.036005844407715</v>
+        <v>-3.005266150259865</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.923682844818817</v>
+        <v>1.935978722477957</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.1207306765431539</v>
+        <v>-0.08999098239530395</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.066003200969758</v>
+        <v>3.084447017458468</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.528390872431812</v>
+        <v>-3.497651178283962</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.727835225652911</v>
+        <v>1.740131103312051</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.5823760104194007</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.771678576199033</v>
+        <v>2.790122392687743</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.913571263361884</v>
+        <v>-3.882831569214034</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.572305608093745</v>
+        <v>1.584601485752885</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.5823760104194007</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.770221115011896</v>
+        <v>2.788664931500606</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.257254036588547</v>
+        <v>-4.226514342440697</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.436601622257696</v>
+        <v>1.448897499916836</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.7210217565944688</v>
+        <v>-0.6902820624466188</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.707246607250181</v>
+        <v>2.725690423738891</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.614904386826895</v>
+        <v>-4.584164692679045</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.289647540818615</v>
+        <v>1.301943418477755</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.078672106832817</v>
+        <v>-1.047932412684967</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.48876245576343</v>
+        <v>2.50720627225214</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.924138489822946</v>
+        <v>-4.893398795675096</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.167726826320454</v>
+        <v>1.180022703979594</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.078672106832817</v>
+        <v>-1.047932412684967</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.49053538246369</v>
+        <v>2.5089791989524</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.355944282972733</v>
+        <v>-5.325204588824883</v>
       </c>
       <c r="E1859" t="n">
-        <v>0.9813373965279433</v>
+        <v>0.9936332741870832</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.215089603274084</v>
+        <v>-1.184349909126234</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.395017772066334</v>
+        <v>2.413461588555044</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.590638277105286</v>
+        <v>-5.559898582957436</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.8757445738770131</v>
+        <v>0.8880404515361531</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.178013641896979</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.387104307405978</v>
+        <v>2.405548123894688</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.926300924335738</v>
+        <v>-5.895561230187888</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7400601066407972</v>
+        <v>0.7523559842999372</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.178013641896979</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.385684899061943</v>
+        <v>2.404128715550653</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.289927169236051</v>
+        <v>-6.259187475088202</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6010971689149134</v>
+        <v>0.6133930465740534</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.306974972911954</v>
+        <v>-1.276235278764104</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.333239477175909</v>
+        <v>2.351683293664619</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.655054551874798</v>
+        <v>-6.624314857726948</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.454300730865246</v>
+        <v>0.466596608524386</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.603285757210967</v>
+        <v>-1.572546063063117</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.154707521602333</v>
+        <v>2.173151338091043</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-7.063643329055477</v>
+        <v>-7.032903634907626</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.2896267640077337</v>
+        <v>0.3019226416668737</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.981134840243795</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.908315799308685</v>
+        <v>1.926759615797395</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.476625813196571</v>
+        <v>-7.44588611904872</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1196192028227565</v>
+        <v>0.1319150804818969</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.981134840243795</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.903501231780145</v>
+        <v>1.921945048268856</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.893017687483568</v>
+        <v>-7.862277993335717</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.04894349628316519</v>
+        <v>-0.03664761862402477</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.981134840243795</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.901495282389023</v>
+        <v>1.919939098877733</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.269694698013412</v>
+        <v>-8.238955003865561</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1893556098264235</v>
+        <v>-0.1770597321672831</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.981134840243795</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.911753973057702</v>
+        <v>1.930197789546412</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.615569519998221</v>
+        <v>-8.58482982585037</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.3316059734746521</v>
+        <v>-0.3193100958155117</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.981134840243795</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.907853538203397</v>
+        <v>1.926297354692107</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.777711790461314</v>
+        <v>-8.746972096313463</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3980579616048883</v>
+        <v>-0.3857620839457478</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.981134840243795</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.906258458258398</v>
+        <v>1.924702274747108</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-9.074373132271512</v>
+        <v>-9.043633438123662</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.5129435223997594</v>
+        <v>-0.500647644740619</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.049877975977674</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.868791552747279</v>
+        <v>1.887235369235989</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.507722240381748</v>
+        <v>-9.476982546233897</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6903094701782564</v>
+        <v>-0.6780135925191164</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.049877975977674</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.864765248212876</v>
+        <v>1.883209064701586</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.890723629124379</v>
+        <v>-9.859983934976528</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.8436121269968933</v>
+        <v>-0.8313162493377528</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.049877975977674</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.864663146891292</v>
+        <v>1.883106963380002</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.0481225093375</v>
+        <v>-10.01738281518965</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9040001631107111</v>
+        <v>-0.8917042854515711</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.207276856190795</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.772795334734849</v>
+        <v>1.791239151223559</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.4076528318415</v>
+        <v>-10.37691313769365</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.042461988814262</v>
+        <v>-1.030166111155121</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.207276856190795</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.778145638032899</v>
+        <v>1.796589454521609</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.73405286050651</v>
+        <v>-10.70331316635866</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.165105980323089</v>
+        <v>-1.152810102663949</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.564416579003658</v>
+        <v>-2.533676884855808</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.590221640791069</v>
+        <v>1.608665457279779</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.95320182858071</v>
+        <v>-10.92246213443286</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.249723816930999</v>
+        <v>-1.237427939271859</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.752825852930005</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.461774010568319</v>
+        <v>1.480217827057029</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.9495109036243</v>
+        <v>-10.91877120947645</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.248247446948435</v>
+        <v>-1.235951569289295</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.752825852930005</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.461774010568319</v>
+        <v>1.480217827057029</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.15376907895416</v>
+        <v>-11.12302938480631</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.324437519961738</v>
+        <v>-1.312141642302598</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.911204491691844</v>
+        <v>-2.880464797543994</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.390703840918569</v>
+        <v>1.409147657407279</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.37180685058534</v>
+        <v>-11.34106715643749</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.407170074129774</v>
+        <v>-1.394874196470633</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.085975259787743</v>
+        <v>-3.055235565639893</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.290323934545465</v>
+        <v>1.308767751034175</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.29833701891789</v>
+        <v>-11.26759732477004</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.362410439969373</v>
+        <v>-1.350114562310233</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.012505428120295</v>
+        <v>-2.981765733972445</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.349777535039355</v>
+        <v>1.368221351528065</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.47346143630444</v>
+        <v>-11.44272174215659</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.417904986176473</v>
+        <v>-1.405609108517333</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.156890151358989</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.259258105354946</v>
+        <v>1.277701921843656</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.70791353031893</v>
+        <v>-11.67717383617108</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.518904988683865</v>
+        <v>-1.506609111024725</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.156890151358989</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.25203894045335</v>
+        <v>1.27048275694206</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.99571737485616</v>
+        <v>-11.96497768070831</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.640698717272736</v>
+        <v>-1.628402839613596</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.475433690044077</v>
+        <v>-3.444693995896227</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.072684442957031</v>
+        <v>1.091128259445741</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.22554182201999</v>
+        <v>-12.19480212787214</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.731512706299711</v>
+        <v>-1.71921682864057</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.638081227114237</v>
+        <v>-3.607341532966387</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9762117105534909</v>
+        <v>0.9946555270422008</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.45757074175625</v>
+        <v>-12.4268310476084</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.821630545565101</v>
+        <v>-1.80933466790596</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.669354230154811</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9416978208695514</v>
+        <v>0.9601416373582614</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.40555522778744</v>
+        <v>-12.37481553363959</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.796834004291174</v>
+        <v>-1.784538126632034</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.669354230154811</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9456881565559523</v>
+        <v>0.9641319730446622</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.54722706951156</v>
+        <v>-12.51648737536371</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.854977967879564</v>
+        <v>-1.842682090220424</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.669354230154811</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9442129296572106</v>
+        <v>0.9626567461459206</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.49763622508672</v>
+        <v>-12.46689653093887</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.820088219944758</v>
+        <v>-1.807792342285618</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.650503079877827</v>
+        <v>-3.619763385729977</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9890208464769832</v>
+        <v>1.007464662965693</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.29848411784963</v>
+        <v>-12.26774442370177</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.753478510696601</v>
+        <v>-1.741182633037461</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.485180553928013</v>
+        <v>-3.454440859780163</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.075163228400188</v>
+        <v>1.093607044888898</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.07263896513021</v>
+        <v>-12.04189927098236</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.653561376572628</v>
+        <v>-1.641265498913488</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.44325387834085</v>
+        <v>-3.412514184193</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.109898306788695</v>
+        <v>1.128342123277405</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.78636415280752</v>
+        <v>-11.75562445865967</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.537912307087491</v>
+        <v>-1.525616429428351</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.44325387834085</v>
+        <v>-3.412514184193</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.111037451344754</v>
+        <v>1.129481267833464</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.83925944085181</v>
+        <v>-11.80851974670395</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.556436648143098</v>
+        <v>-1.544140770483958</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.438298532252404</v>
+        <v>-3.407558838104554</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.116644433159929</v>
+        <v>1.135088249648639</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.55535070992306</v>
+        <v>-11.52461101577521</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.437139451532962</v>
+        <v>-1.424843573873821</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.438298532252404</v>
+        <v>-3.407558838104554</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.122378137398566</v>
+        <v>1.140821953887276</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.43992978578496</v>
+        <v>-11.40919009163711</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.400708344271589</v>
+        <v>-1.388412466612449</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.322877608114308</v>
+        <v>-3.292137913966458</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.181893429487558</v>
+        <v>1.200337245976268</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.17609291858089</v>
+        <v>-11.14535322443304</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.305057078702868</v>
+        <v>-1.292761201043728</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.322877608114308</v>
+        <v>-3.292137913966458</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.17200994817465</v>
+        <v>1.19045376466336</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.90885111771249</v>
+        <v>-10.87811142356464</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.199994918854884</v>
+        <v>-1.187699041195743</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.322877608114308</v>
+        <v>-3.292137913966458</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.170175387675277</v>
+        <v>1.188619204163987</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.78554518923427</v>
+        <v>-10.75480549508642</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.150972862437057</v>
+        <v>-1.138676984777916</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.233459936986745</v>
+        <v>-3.202720242838895</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.223525675378353</v>
+        <v>1.241969491867063</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.76159164825832</v>
+        <v>-10.73085195411046</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.14072293990118</v>
+        <v>-1.128427062242039</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.209506396010788</v>
+        <v>-3.178766701862938</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.238566306109422</v>
+        <v>1.257010122598132</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.49753170993552</v>
+        <v>-10.46679201578767</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.048359280733813</v>
+        <v>-1.036063403074673</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.945446457687992</v>
+        <v>-2.914706763540142</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.383741952941347</v>
+        <v>1.402185769430057</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.790452086430681</v>
+        <v>-9.759712392282831</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7683144649921791</v>
+        <v>-0.7560185873330387</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.945446457687992</v>
+        <v>-2.914706763540142</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.380954919281046</v>
+        <v>1.399398735769756</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.750267788064491</v>
+        <v>-9.71952809391664</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7518971217578616</v>
+        <v>-0.7396012440987212</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.905262159321801</v>
+        <v>-2.874522465173951</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.405409122188602</v>
+        <v>1.423852938677312</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.670197992526687</v>
+        <v>-9.639458298378836</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7205023823219827</v>
+        <v>-0.7082065046628423</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.825192363783997</v>
+        <v>-2.794452669636147</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.452817820732042</v>
+        <v>1.471261637220752</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.436716770297089</v>
+        <v>-9.405977076149238</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6191854645922912</v>
+        <v>-0.6068895869331508</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.591711141554398</v>
+        <v>-2.560971447406548</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.600830982907653</v>
+        <v>1.619274799396363</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.257008240153215</v>
+        <v>-9.226268546005365</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5501942628477012</v>
+        <v>-0.5378983851885608</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.534539637391702</v>
+        <v>-2.503799943243852</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.632241675092311</v>
+        <v>1.650685491581021</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.124732766522328</v>
+        <v>-9.093993072374477</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5019165866483193</v>
+        <v>-0.4896207089891789</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.402264163760816</v>
+        <v>-2.371524469612966</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.70697444601787</v>
+        <v>1.72541826250658</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.934133091849175</v>
+        <v>-8.903393397701324</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4228616560914209</v>
+        <v>-0.4105657784322805</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.211664489087663</v>
+        <v>-2.180924794939813</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.824149311509399</v>
+        <v>1.842593127998109</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.685133293165594</v>
+        <v>-8.654393599017743</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3103553953943297</v>
+        <v>-0.2980595177351897</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.211664489087663</v>
+        <v>-2.180924794939813</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.837055652733057</v>
+        <v>1.855499469221767</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.790723282938698</v>
+        <v>-8.759983588790847</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4805673209027903</v>
+        <v>-0.4682714432436499</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.317254478860768</v>
+        <v>-2.286514784712918</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.645725729269976</v>
+        <v>1.664169545758686</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.809458185057295</v>
+        <v>-8.778718490909444</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4395169398731427</v>
+        <v>-0.4272210622140022</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.317254478860768</v>
+        <v>-2.286514784712918</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.694270071147062</v>
+        <v>1.712713887635772</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.661518143649696</v>
+        <v>-8.630778449501845</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5002198459982705</v>
+        <v>-0.4879239683391301</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.29693356295221</v>
+        <v>-2.26619386880436</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.58658369800403</v>
+        <v>1.60502751449274</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.637289507260723</v>
+        <v>-8.606549813112872</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4992423776961599</v>
+        <v>-0.4869465000370194</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.272704926563238</v>
+        <v>-2.241965232415388</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.592406893583935</v>
+        <v>1.610850710072645</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.593741100490032</v>
+        <v>-8.563001406342181</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4887836270829764</v>
+        <v>-0.476487749423836</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.272704926563238</v>
+        <v>-2.241965232415388</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.585446281488841</v>
+        <v>1.603890097977551</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.351592707036174</v>
+        <v>-8.320853012888323</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3774619153202901</v>
+        <v>-0.3651660376611496</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.272704926563238</v>
+        <v>-2.241965232415388</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.599908635869985</v>
+        <v>1.618352452358695</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.288363335267826</v>
+        <v>-8.257623641119975</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3576380461537561</v>
+        <v>-0.3453421684946156</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.272704926563238</v>
+        <v>-2.241965232415388</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.59444075632918</v>
+        <v>1.61288457281789</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.165072200450696</v>
+        <v>-8.134332506302846</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3108234982163274</v>
+        <v>-0.298527620557187</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.149413791746107</v>
+        <v>-2.118674097598257</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.665913531230035</v>
+        <v>1.684357347718745</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.143923001547254</v>
+        <v>-8.113183307399403</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.294662840417625</v>
+        <v>-0.2823669627584846</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.128264592842664</v>
+        <v>-2.097524898694814</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.686304028809426</v>
+        <v>1.704747845298136</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.90015755956381</v>
+        <v>-7.869417865415959</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2013759552771965</v>
+        <v>-0.1890800776180561</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.128264592842664</v>
+        <v>-2.097524898694814</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.682084737156476</v>
+        <v>1.700528553645186</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.63612949237055</v>
+        <v>-7.605389798222699</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.09364041447987681</v>
+        <v>-0.08134453682073639</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.92639919402671</v>
+        <v>-1.895659499878861</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.805328290366065</v>
+        <v>1.823772106854775</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.479365989750649</v>
+        <v>-7.355539404273625</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.03819293844821425</v>
+        <v>0.01133769574259569</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.92639919402671</v>
+        <v>-1.895659499878861</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.798070365349767</v>
+        <v>1.816514181838477</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.17579850074667</v>
+        <v>-7.051971915269646</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.0868331806740259</v>
+        <v>0.1363638148648358</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.92639919402671</v>
+        <v>-1.895659499878861</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.801669488870415</v>
+        <v>1.820113305359125</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.102318591894656</v>
+        <v>-6.978492006417632</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1295526502693853</v>
+        <v>0.1790832844601948</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.852919285174696</v>
+        <v>-1.822179591026846</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.859084940236178</v>
+        <v>1.877528756724888</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.877285592225833</v>
+        <v>-6.753459006748809</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2185863277532114</v>
+        <v>0.2681169619440213</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.627886285505873</v>
+        <v>-1.597146591358023</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.993125217653768</v>
+        <v>2.011569034142478</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.662651214589427</v>
+        <v>-6.538824629112402</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3091348798620914</v>
+        <v>0.3586655140529014</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.413251907869467</v>
+        <v>-1.382512213721617</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.12660064528993</v>
+        <v>2.14504446177864</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.396050857615075</v>
+        <v>-6.27222427213805</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3969692814356276</v>
+        <v>0.4464999156264375</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.413251907869467</v>
+        <v>-1.382512213721617</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.107794904073725</v>
+        <v>2.126238720562435</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.155620360810214</v>
+        <v>-6.03179377533319</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4948845567824494</v>
+        <v>0.5444151909732589</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.172821411064606</v>
+        <v>-1.142081716916756</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.253796278781519</v>
+        <v>2.272240095270229</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.912829553160769</v>
+        <v>-5.789002967683745</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5959301936770478</v>
+        <v>0.6454608278678573</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.172821411064606</v>
+        <v>-1.142081716916756</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.257725592616339</v>
+        <v>2.276169409105049</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.796889703535584</v>
+        <v>-5.673063118058559</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6429847174444618</v>
+        <v>0.6925153516352718</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.095999680048482</v>
+        <v>-1.065259985900632</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.304497215143353</v>
+        <v>2.322941031632063</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.55423411511242</v>
+        <v>-5.430407529635396</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.737045024033721</v>
+        <v>0.7865756582245305</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.095999680048482</v>
+        <v>-1.065259985900632</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.301495286363347</v>
+        <v>2.319939102852057</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.33421331707541</v>
+        <v>-5.210386731598385</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8266323802591393</v>
+        <v>0.8761630144499488</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9547798349805021</v>
+        <v>-0.9240401408326522</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.387806230414749</v>
+        <v>2.406250046903459</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.134964687170601</v>
+        <v>-5.011138101693576</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9222260150228863</v>
+        <v>0.9717566492136958</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9547798349805021</v>
+        <v>-0.9240401408326522</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.403700413216573</v>
+        <v>2.422144229705283</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.975449583651231</v>
+        <v>-4.851622998174206</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9871779008709358</v>
+        <v>1.036708535061746</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7952647314611322</v>
+        <v>-0.7645250373132823</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.500555319768496</v>
+        <v>2.518999136257206</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.830777438551493</v>
+        <v>-4.706950853074469</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.055134861472271</v>
+        <v>1.104665495663081</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6505925863613948</v>
+        <v>-0.6198528922135449</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.597446709389779</v>
+        <v>2.615890525878489</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.890652265909186</v>
+        <v>-4.766825680432161</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.01722242193062</v>
+        <v>1.066753056121429</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7104674137190869</v>
+        <v>-0.679727719571237</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.547559304376589</v>
+        <v>2.566003120865299</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.803852768130177</v>
+        <v>-4.680026182653153</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.074342714364789</v>
+        <v>1.123873348555599</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7104674137190869</v>
+        <v>-0.679727719571237</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.569959797699156</v>
+        <v>2.588403614187865</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.806322474591983</v>
+        <v>-4.682495889114959</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.073427233153479</v>
+        <v>1.122957867344289</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.7129371201808932</v>
+        <v>-0.6821974260330432</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.568550375195484</v>
+        <v>2.586994191684194</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.874692660915994</v>
+        <v>-4.750866075438969</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.057086081098577</v>
+        <v>1.106616715289386</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.7036614211446782</v>
+        <v>-0.6729217269968283</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.585122717091915</v>
+        <v>2.603566533580625</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.753276231289517</v>
+        <v>-4.629449645812493</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.096089361581059</v>
+        <v>1.145619995771868</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.7036614211446782</v>
+        <v>-0.6729217269968283</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.575559425723806</v>
+        <v>2.594003242212516</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.784269390618222</v>
+        <v>-4.660442805141198</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9084016628899634</v>
+        <v>0.9579322970807731</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.7036614211446782</v>
+        <v>-0.6729217269968283</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.400268990764193</v>
+        <v>2.418712807252903</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.608795130825753</v>
+        <v>-4.484968545348728</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.983158598798739</v>
+        <v>1.032689232989549</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.7036614211446782</v>
+        <v>-0.6729217269968283</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.404836222755981</v>
+        <v>2.423280039244691</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.719731383467002</v>
+        <v>-4.595904797989977</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9387955716290368</v>
+        <v>0.9883262058198468</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.7036614211446782</v>
+        <v>-0.6729217269968283</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.404847696642778</v>
+        <v>2.423291513131488</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.922757961010235</v>
+        <v>-4.79893137553321</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8607163258316493</v>
+        <v>0.910246960022459</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.9066879986879116</v>
+        <v>-0.8759483045400617</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.286163135336744</v>
+        <v>2.304606951825454</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.764832362074942</v>
+        <v>-4.641005776597917</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9340589518378988</v>
+        <v>0.9835895860287085</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.9066879986879116</v>
+        <v>-0.8759483045400617</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.296335521768876</v>
+        <v>2.314779338257586</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.91315361588607</v>
+        <v>-4.789327030409046</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8696767208873075</v>
+        <v>0.9192073550781172</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.9066879986879116</v>
+        <v>-0.8759483045400617</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.291281792342736</v>
+        <v>2.309725608831446</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.914336700537131</v>
+        <v>-4.790510115060107</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.860979262471409</v>
+        <v>0.9105098966622187</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.9123310471544231</v>
+        <v>-0.8815913530065732</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.279671738707355</v>
+        <v>2.298115555196065</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.791208993543048</v>
+        <v>-4.667382408066024</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9107822183021437</v>
+        <v>0.9603128524929534</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.9123310471544231</v>
+        <v>-0.8815913530065732</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.280223611740456</v>
+        <v>2.298667428229166</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.698398512092188</v>
+        <v>-4.574571926615164</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8771791027738531</v>
+        <v>0.9267097369646629</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8195205657035638</v>
+        <v>-0.7887808715557139</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.265182592502338</v>
+        <v>2.283626408991048</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.649835459871158</v>
+        <v>-4.526008874394134</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.898477799586866</v>
+        <v>0.9480084337776757</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.7709575134825336</v>
+        <v>-0.7402178193346837</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.296193899759557</v>
+        <v>2.314637716248267</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.537164241634908</v>
+        <v>-4.413337656157884</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.938621995393089</v>
+        <v>0.9881526295838987</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.6582862952462833</v>
+        <v>-0.6275466010984334</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.35887233921303</v>
+        <v>2.37731615570174</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.424787240452235</v>
+        <v>-4.300960654975211</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9890640916968254</v>
+        <v>1.038594725887635</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.6582862952462833</v>
+        <v>-0.6275466010984334</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.364363635043697</v>
+        <v>2.382807451532407</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.623021809338966</v>
+        <v>-4.499195223861942</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9212674659106721</v>
+        <v>0.970798100101482</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.856520864133014</v>
+        <v>-0.825781169985164</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.256920095480198</v>
+        <v>2.275363911968908</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.381690605938775</v>
+        <v>3.742277745139008</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.649309575323622</v>
+        <v>2.80860554709678</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.623021809338966</v>
+        <v>-4.499195223861942</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9212674659106721</v>
+        <v>0.970798100101482</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.856520864133014</v>
+        <v>-0.825781169985164</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.64237337230999</v>
+        <v>2.801669344083148</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240501.xlsx
+++ b/tame_output/ON/bt/strategyON_20240501.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-46.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.7%</t>
+          <t>-81.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.1%</t>
+          <t>117.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.3%</t>
+          <t>137.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>-58.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.3%</t>
+          <t>440.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-611.5%</t>
+          <t>-623.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-45.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-63.2%</t>
+          <t>-81.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.1%</t>
+          <t>-285.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-163.2%</t>
+          <t>-165.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-306.6%</t>
+          <t>-321.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-165.9%</t>
+          <t>-182.0%</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.26774442370177</v>
+        <v>-12.36941509139199</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.741182633037461</v>
+        <v>-1.781850900113548</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.454440859780163</v>
+        <v>-3.583522111358982</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.093607044888898</v>
+        <v>1.016158293941607</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.04189927098236</v>
+        <v>-12.14356993867258</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.641265498913488</v>
+        <v>-1.681933765989575</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.412514184193</v>
+        <v>-3.541595435771819</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.128342123277405</v>
+        <v>1.050893372330114</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.75562445865967</v>
+        <v>-11.85729512634989</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.525616429428351</v>
+        <v>-1.566284696504438</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.412514184193</v>
+        <v>-3.541595435771819</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.129481267833464</v>
+        <v>1.052032516886173</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.80851974670395</v>
+        <v>-11.91019041439417</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.544140770483958</v>
+        <v>-1.584809037560045</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.407558838104554</v>
+        <v>-3.536640089683373</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.135088249648639</v>
+        <v>1.057639498701348</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.52461101577521</v>
+        <v>-11.62628168346542</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.424843573873821</v>
+        <v>-1.465511840949909</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.407558838104554</v>
+        <v>-3.536640089683373</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.140821953887276</v>
+        <v>1.063373202939985</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.40919009163711</v>
+        <v>-11.51086075932733</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.388412466612449</v>
+        <v>-1.429080733688536</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.292137913966458</v>
+        <v>-3.421219165545277</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.200337245976268</v>
+        <v>1.122888495028977</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.14535322443304</v>
+        <v>-11.24702389212326</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.292761201043728</v>
+        <v>-1.333429468119815</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.292137913966458</v>
+        <v>-3.421219165545277</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.19045376466336</v>
+        <v>1.113005013716069</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.87811142356464</v>
+        <v>-10.97978209125486</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.187699041195743</v>
+        <v>-1.22836730827183</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.292137913966458</v>
+        <v>-3.421219165545277</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.188619204163987</v>
+        <v>1.111170453216695</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.75480549508642</v>
+        <v>-10.85647616277664</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.138676984777916</v>
+        <v>-1.179345251854004</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.202720242838895</v>
+        <v>-3.331801494417714</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.241969491867063</v>
+        <v>1.164520740919772</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.73085195411046</v>
+        <v>-10.83252262180068</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.128427062242039</v>
+        <v>-1.169095329318127</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.178766701862938</v>
+        <v>-3.307847953441756</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.257010122598132</v>
+        <v>1.17956137165084</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.46679201578767</v>
+        <v>-10.56846268347789</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.036063403074673</v>
+        <v>-1.07673167015076</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.914706763540142</v>
+        <v>-3.04378801511896</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.402185769430057</v>
+        <v>1.324737018482766</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.759712392282831</v>
+        <v>-9.861383059973049</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7560185873330387</v>
+        <v>-0.7966868544091259</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.914706763540142</v>
+        <v>-3.04378801511896</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.399398735769756</v>
+        <v>1.321949984822465</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.71952809391664</v>
+        <v>-9.821198761606858</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7396012440987212</v>
+        <v>-0.7802695111748084</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.874522465173951</v>
+        <v>-3.003603716752769</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.423852938677312</v>
+        <v>1.346404187730021</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.639458298378836</v>
+        <v>-9.741128966069054</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7082065046628423</v>
+        <v>-0.7488747717389295</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.794452669636147</v>
+        <v>-2.923533921214965</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.471261637220752</v>
+        <v>1.39381288627346</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.405977076149238</v>
+        <v>-9.507647743839456</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6068895869331508</v>
+        <v>-0.6475578540092384</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.560971447406548</v>
+        <v>-2.690052698985367</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.619274799396363</v>
+        <v>1.541826048449072</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.226268546005365</v>
+        <v>-9.327939213695583</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5378983851885608</v>
+        <v>-0.578566652264648</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.503799943243852</v>
+        <v>-2.632881194822671</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.650685491581021</v>
+        <v>1.57323674063373</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.093993072374477</v>
+        <v>-9.195663740064695</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4896207089891789</v>
+        <v>-0.530288976065266</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.371524469612966</v>
+        <v>-2.500605721191784</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.72541826250658</v>
+        <v>1.647969511559289</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.903393397701324</v>
+        <v>-9.005064065391542</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4105657784322805</v>
+        <v>-0.4512340455083681</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.180924794939813</v>
+        <v>-2.310006046518632</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.842593127998109</v>
+        <v>1.765144377050818</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.654393599017743</v>
+        <v>-8.756064266707961</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2980595177351897</v>
+        <v>-0.3387277848112769</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.180924794939813</v>
+        <v>-2.310006046518632</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.855499469221767</v>
+        <v>1.778050718274476</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.759983588790847</v>
+        <v>-8.861654256481065</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4682714432436499</v>
+        <v>-0.5089397103197371</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.286514784712918</v>
+        <v>-2.415596036291736</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.664169545758686</v>
+        <v>1.586720794811395</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.778718490909444</v>
+        <v>-8.880389158599662</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4272210622140022</v>
+        <v>-0.4678893292900899</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.286514784712918</v>
+        <v>-2.415596036291736</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.712713887635772</v>
+        <v>1.635265136688481</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.630778449501845</v>
+        <v>-8.732449117192063</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4879239683391301</v>
+        <v>-0.5285922354152177</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.26619386880436</v>
+        <v>-2.395275120383178</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.60502751449274</v>
+        <v>1.527578763545448</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.606549813112872</v>
+        <v>-8.708220480803091</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4869465000370194</v>
+        <v>-0.5276147671131066</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.241965232415388</v>
+        <v>-2.371046483994206</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.610850710072645</v>
+        <v>1.533401959125353</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.563001406342181</v>
+        <v>-8.664672074032399</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.476487749423836</v>
+        <v>-0.5171560164999232</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.241965232415388</v>
+        <v>-2.371046483994206</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.603890097977551</v>
+        <v>1.52644134703026</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.320853012888323</v>
+        <v>-8.422523680578541</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3651660376611496</v>
+        <v>-0.4058343047372368</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.241965232415388</v>
+        <v>-2.371046483994206</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.618352452358695</v>
+        <v>1.540903701411403</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.257623641119975</v>
+        <v>-8.359294308810194</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3453421684946156</v>
+        <v>-0.3860104355707028</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.241965232415388</v>
+        <v>-2.371046483994206</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.61288457281789</v>
+        <v>1.535435821870598</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.134332506302846</v>
+        <v>-8.236003173993064</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.298527620557187</v>
+        <v>-0.3391958876332741</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.118674097598257</v>
+        <v>-2.247755349177076</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.684357347718745</v>
+        <v>1.606908596771454</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.113183307399403</v>
+        <v>-8.214853975089621</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2823669627584846</v>
+        <v>-0.3230352298345718</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.097524898694814</v>
+        <v>-2.226606150273633</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.704747845298136</v>
+        <v>1.627299094350845</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.869417865415959</v>
+        <v>-7.971088533106177</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1890800776180561</v>
+        <v>-0.2297483446941437</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.097524898694814</v>
+        <v>-2.226606150273633</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.700528553645186</v>
+        <v>1.623079802697895</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.605389798222699</v>
+        <v>-7.707060465912917</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.08134453682073639</v>
+        <v>-0.1220128038968236</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.895659499878861</v>
+        <v>-2.024740751457679</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.823772106854775</v>
+        <v>1.746323355907483</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.355539404273625</v>
+        <v>-7.457210071963843</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.01133769574259569</v>
+        <v>-0.02933057133349193</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.895659499878861</v>
+        <v>-2.024740751457679</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.816514181838477</v>
+        <v>1.739065430891185</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.051971915269646</v>
+        <v>-7.153642582959864</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1363638148648358</v>
+        <v>0.09569554778874867</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.895659499878861</v>
+        <v>-2.024740751457679</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.820113305359125</v>
+        <v>1.742664554411834</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.978492006417632</v>
+        <v>-7.08016267410785</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1790832844601948</v>
+        <v>0.1384150173841077</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.822179591026846</v>
+        <v>-1.951260842605665</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.877528756724888</v>
+        <v>1.800080005777597</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.753459006748809</v>
+        <v>-6.855129674439027</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2681169619440213</v>
+        <v>0.2274486948679337</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.597146591358023</v>
+        <v>-1.726227842936842</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.011569034142478</v>
+        <v>1.934120283195187</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.538824629112402</v>
+        <v>-6.64049529680262</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3586655140529014</v>
+        <v>0.3179972469768138</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.382512213721617</v>
+        <v>-1.511593465300435</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.14504446177864</v>
+        <v>2.067595710831349</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.27222427213805</v>
+        <v>-6.373894939828268</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4464999156264375</v>
+        <v>0.4058316485503504</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.382512213721617</v>
+        <v>-1.511593465300435</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.126238720562435</v>
+        <v>2.048789969615144</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.03179377533319</v>
+        <v>-6.133464443023408</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5444151909732589</v>
+        <v>0.5037469238971717</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.142081716916756</v>
+        <v>-1.271162968495575</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.272240095270229</v>
+        <v>2.194791344322938</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.789002967683745</v>
+        <v>-5.890673635373963</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6454608278678573</v>
+        <v>0.6047925607917701</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.142081716916756</v>
+        <v>-1.271162968495575</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.276169409105049</v>
+        <v>2.198720658157758</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.673063118058559</v>
+        <v>-5.774733785748777</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6925153516352718</v>
+        <v>0.6518470845591842</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.065259985900632</v>
+        <v>-1.194341237479451</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.322941031632063</v>
+        <v>2.245492280684772</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.430407529635396</v>
+        <v>-5.532078197325614</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7865756582245305</v>
+        <v>0.7459073911484433</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.065259985900632</v>
+        <v>-1.194341237479451</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.319939102852057</v>
+        <v>2.242490351904766</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.210386731598385</v>
+        <v>-5.312057399288603</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8761630144499488</v>
+        <v>0.8354947473738616</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9240401408326522</v>
+        <v>-1.053121392411471</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.406250046903459</v>
+        <v>2.328801295956168</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.011138101693576</v>
+        <v>-5.112808769383794</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9717566492136958</v>
+        <v>0.9310883821376086</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9240401408326522</v>
+        <v>-1.053121392411471</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.422144229705283</v>
+        <v>2.344695478757991</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.851622998174206</v>
+        <v>-4.953293665864424</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.036708535061746</v>
+        <v>0.9960402679856584</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7645250373132823</v>
+        <v>-0.8936062888921007</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.518999136257206</v>
+        <v>2.441550385309915</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.706950853074469</v>
+        <v>-4.808621520764687</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.104665495663081</v>
+        <v>1.063997228586993</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6198528922135449</v>
+        <v>-0.7489341437923633</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.615890525878489</v>
+        <v>2.538441774931198</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.766825680432161</v>
+        <v>-4.868496348122379</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.066753056121429</v>
+        <v>1.026084789045342</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.679727719571237</v>
+        <v>-0.8088089711500555</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.566003120865299</v>
+        <v>2.488554369918008</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.680026182653153</v>
+        <v>-4.781696850343371</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.123873348555599</v>
+        <v>1.083205081479512</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.679727719571237</v>
+        <v>-0.8088089711500555</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.588403614187865</v>
+        <v>2.510954863240574</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.682495889114959</v>
+        <v>-4.784166556805177</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.122957867344289</v>
+        <v>1.082289600268201</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6821974260330432</v>
+        <v>-0.8112786776118617</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.586994191684194</v>
+        <v>2.509545440736903</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.007319569778721</v>
+        <v>2.989623696939967</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.750866075438969</v>
+        <v>-4.852536743129187</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.106616715289386</v>
+        <v>1.048252575374545</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6729217269968283</v>
+        <v>-0.8020029785756467</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.603566533580625</v>
+        <v>2.508421909794579</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.997756278410613</v>
+        <v>2.980060405571859</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.629449645812493</v>
+        <v>-4.731120313502711</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.145619995771868</v>
+        <v>1.087255855857027</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6729217269968283</v>
+        <v>-0.8020029785756467</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.594003242212516</v>
+        <v>2.498858618426471</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>2.804769970612246</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.660442805141198</v>
+        <v>-4.762113472831416</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9579322970807731</v>
+        <v>0.8995681571659317</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6729217269968283</v>
+        <v>-0.8020029785756467</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.418712807252903</v>
+        <v>2.323568183466858</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>2.809337202604033</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.484968545348728</v>
+        <v>-4.586639213038946</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.032689232989549</v>
+        <v>0.9743250930747074</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6729217269968283</v>
+        <v>-0.8020029785756467</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.423280039244691</v>
+        <v>2.328135415458646</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695447</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.827044549329585</v>
+        <v>2.809348676490831</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.595904797989977</v>
+        <v>-4.697575465680195</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9883262058198468</v>
+        <v>0.9299620659050054</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6729217269968283</v>
+        <v>-0.8020029785756467</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.423291513131488</v>
+        <v>2.328146889345443</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.83017593454949</v>
+        <v>2.812480061710736</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.79893137553321</v>
+        <v>-4.900602043223429</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.910246960022459</v>
+        <v>0.8518828201076176</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8759483045400617</v>
+        <v>-1.00502955611888</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.304606951825454</v>
+        <v>2.209462328039408</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.78434037673416</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.840348320981623</v>
+        <v>2.822652448142869</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.641005776597917</v>
+        <v>-4.742676444288136</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9835895860287085</v>
+        <v>0.9252254461138674</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8759483045400617</v>
+        <v>-1.00502955611888</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.314779338257586</v>
+        <v>2.219634714471541</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212296</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.835294591555483</v>
+        <v>2.817598718716729</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.789327030409046</v>
+        <v>-4.890997698099264</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9192073550781172</v>
+        <v>0.8608432151632761</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8759483045400617</v>
+        <v>-1.00502955611888</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.309725608831446</v>
+        <v>2.214580985045401</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.827070367000009</v>
+        <v>2.809374494161255</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.790510115060107</v>
+        <v>-4.892180782750325</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9105098966622187</v>
+        <v>0.8521457567473774</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8815913530065732</v>
+        <v>-1.010672604585392</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.298115555196065</v>
+        <v>2.20297093141002</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.82762224003311</v>
+        <v>2.809926367194356</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.667382408066024</v>
+        <v>-4.769053075756242</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9603128524929534</v>
+        <v>0.9019487125781123</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8815913530065732</v>
+        <v>-1.010672604585392</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.298667428229166</v>
+        <v>2.203522804443121</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.756894931924476</v>
+        <v>2.739199059085722</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.574571926615164</v>
+        <v>-4.676242594305382</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9267097369646629</v>
+        <v>0.8683455970498217</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7887808715557139</v>
+        <v>-0.9178621231345324</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.283626408991048</v>
+        <v>2.188481785205003</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.758768407849077</v>
+        <v>2.741072535010323</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.526008874394134</v>
+        <v>-4.627679542084352</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9480084337776757</v>
+        <v>0.8896442938628346</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.7402178193346837</v>
+        <v>-0.8692990709135022</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.314637716248267</v>
+        <v>2.219493092462222</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.7538441163608</v>
+        <v>2.736148243522046</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.413337656157884</v>
+        <v>-4.515008323848102</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9881526295838987</v>
+        <v>0.9297884896690576</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.6275466010984334</v>
+        <v>-0.756627852677252</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.37731615570174</v>
+        <v>2.282171531915695</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.759335412191467</v>
+        <v>2.741639539352713</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.300960654975211</v>
+        <v>-4.402631322665429</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.038594725887635</v>
+        <v>0.980230585972794</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.6275466010984334</v>
+        <v>-0.756627852677252</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.382807451532407</v>
+        <v>2.287662827746362</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.770832613960006</v>
+        <v>2.753136741121252</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.499195223861942</v>
+        <v>-4.621094093151122</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.970798100101482</v>
+        <v>0.9043426795470559</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.825781169985164</v>
+        <v>-0.975090623162945</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.275363911968908</v>
+        <v>2.168082367223485</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.742277745139008</v>
+        <v>3.379769649168515</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.80860554709678</v>
+        <v>2.647346843331023</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.499195223861942</v>
+        <v>-4.621094093151122</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.970798100101482</v>
+        <v>0.9043426795470559</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.825781169985164</v>
+        <v>-0.975090623162945</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.801669344083148</v>
+        <v>2.640410640317391</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240501.xlsx
+++ b/tame_output/ON/bt/strategyON_20240501.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-34.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.1%</t>
+          <t>-81.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.0%</t>
+          <t>116.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.5%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-717.6%</t>
+          <t>-706.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.3%</t>
+          <t>-56.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.6%</t>
+          <t>444.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-623.7%</t>
+          <t>-624.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-287.4%</t>
+          <t>-282.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.6%</t>
+          <t>-42.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-81.6%</t>
+          <t>-63.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-285.8%</t>
+          <t>-284.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-36.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,17 +1293,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-341.8%</t>
+          <t>-330.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-165.7%</t>
+          <t>-160.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-321.5%</t>
+          <t>-317.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-205.5%</t>
+          <t>-198.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1461,52 +1461,52 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-182.0%</t>
+          <t>-224.7%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.844765679408686</v>
+        <v>-1.875505373556535</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.378657571364643</v>
+        <v>2.366361693705503</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.682170731160316</v>
+        <v>0.6514310370124661</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.526222706138054</v>
+        <v>3.507778889649344</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.183924056997208</v>
+        <v>-2.070845918412017</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.236078519635683</v>
+        <v>2.28130977506976</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3430123535717939</v>
+        <v>0.4560904921569849</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.31581197889139</v>
+        <v>3.383658862042505</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.511941278724687</v>
+        <v>-2.398863140139496</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.12520992068346</v>
+        <v>2.170441176117536</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.01499513184431478</v>
+        <v>0.1280732704295057</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.139339935593671</v>
+        <v>3.207186818744785</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.005266150259865</v>
+        <v>-2.892188011674674</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.935978722477957</v>
+        <v>1.981209977912034</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.08999098239530395</v>
+        <v>0.02308715618988699</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.084447017458468</v>
+        <v>3.152293900609583</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.497651178283962</v>
+        <v>-3.384573039698771</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.740131103312051</v>
+        <v>1.785362358746127</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.5823760104194007</v>
+        <v>-0.4692978718342097</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.790122392687743</v>
+        <v>2.857969275838857</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.882831569214034</v>
+        <v>-3.769753430628843</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.584601485752885</v>
+        <v>1.629832741186961</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.5823760104194007</v>
+        <v>-0.4692978718342097</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.788664931500606</v>
+        <v>2.856511814651721</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.226514342440697</v>
+        <v>-4.113436203855506</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.448897499916836</v>
+        <v>1.494128755350912</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.6902820624466188</v>
+        <v>-0.5772039238614279</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.725690423738891</v>
+        <v>2.793537306890006</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.584164692679045</v>
+        <v>-4.471086554093854</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.301943418477755</v>
+        <v>1.347174673911831</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.047932412684967</v>
+        <v>-0.9348542740997761</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.50720627225214</v>
+        <v>2.575053155403254</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.893398795675096</v>
+        <v>-4.780320657089905</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.180022703979594</v>
+        <v>1.22525395941367</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.047932412684967</v>
+        <v>-0.9348542740997761</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.5089791989524</v>
+        <v>2.576826082103514</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.325204588824883</v>
+        <v>-5.212126450239692</v>
       </c>
       <c r="E1859" t="n">
-        <v>0.9936332741870832</v>
+        <v>1.03886452962116</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.184349909126234</v>
+        <v>-1.071271770541043</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.413461588555044</v>
+        <v>2.481308471706158</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.559898582957436</v>
+        <v>-5.446820444372245</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.8880404515361531</v>
+        <v>0.9332717069702294</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.178013641896979</v>
+        <v>-1.064935503311788</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.405548123894688</v>
+        <v>2.473395007045802</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.895561230187888</v>
+        <v>-5.782483091602697</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7523559842999372</v>
+        <v>0.7975872397340136</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.178013641896979</v>
+        <v>-1.064935503311788</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.404128715550653</v>
+        <v>2.471975598701767</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.259187475088202</v>
+        <v>-6.14610933650301</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6133930465740534</v>
+        <v>0.6586243020081297</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.276235278764104</v>
+        <v>-1.163157140178914</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.351683293664619</v>
+        <v>2.419530176815733</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.624314857726948</v>
+        <v>-6.511236719141757</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.466596608524386</v>
+        <v>0.5118278639584624</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.572546063063117</v>
+        <v>-1.459467924477926</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.173151338091043</v>
+        <v>2.240998221242157</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-7.032903634907626</v>
+        <v>-6.919825496322435</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3019226416668737</v>
+        <v>0.3471538971009505</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.981134840243795</v>
+        <v>-1.868056701658605</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.926759615797395</v>
+        <v>1.994606498948509</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.44588611904872</v>
+        <v>-7.332807980463529</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1319150804818969</v>
+        <v>0.1771463359159733</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.981134840243795</v>
+        <v>-1.868056701658605</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.921945048268856</v>
+        <v>1.98979193141997</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.862277993335717</v>
+        <v>-7.749199854750526</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.03664761862402477</v>
+        <v>0.008583636810051587</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.981134840243795</v>
+        <v>-1.868056701658605</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.919939098877733</v>
+        <v>1.987785982028847</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.238955003865561</v>
+        <v>-8.12587686528037</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1770597321672831</v>
+        <v>-0.1318284767332067</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.981134840243795</v>
+        <v>-1.868056701658605</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.930197789546412</v>
+        <v>1.998044672697526</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.58482982585037</v>
+        <v>-8.471751687265179</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.3193100958155117</v>
+        <v>-0.2740788403814354</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.981134840243795</v>
+        <v>-1.868056701658605</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.926297354692107</v>
+        <v>1.994144237843221</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.746972096313463</v>
+        <v>-8.633893957728272</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3857620839457478</v>
+        <v>-0.3405308285116715</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.981134840243795</v>
+        <v>-1.868056701658605</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.924702274747108</v>
+        <v>1.992549157898222</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-9.043633438123662</v>
+        <v>-8.93055529953847</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.500647644740619</v>
+        <v>-0.4554163893065426</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.049877975977674</v>
+        <v>-1.936799837392483</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.887235369235989</v>
+        <v>1.955082252387103</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.476982546233897</v>
+        <v>-9.363904407648706</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6780135925191164</v>
+        <v>-0.6327823370850396</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.049877975977674</v>
+        <v>-1.936799837392483</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.883209064701586</v>
+        <v>1.9510559478527</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.859983934976528</v>
+        <v>-9.746905796391337</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.8313162493377528</v>
+        <v>-0.7860849939036765</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.049877975977674</v>
+        <v>-1.936799837392483</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.883106963380002</v>
+        <v>1.950953846531116</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.01738281518965</v>
+        <v>-9.904304676604458</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8917042854515711</v>
+        <v>-0.8464730300174943</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.207276856190795</v>
+        <v>-2.094198717605604</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.791239151223559</v>
+        <v>1.859086034374674</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.37691313769365</v>
+        <v>-10.26383499910846</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.030166111155121</v>
+        <v>-0.9849348557210451</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.207276856190795</v>
+        <v>-2.094198717605604</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.796589454521609</v>
+        <v>1.864436337672724</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.70331316635866</v>
+        <v>-10.59023502777347</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.152810102663949</v>
+        <v>-1.107578847229873</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.533676884855808</v>
+        <v>-2.420598746270617</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.608665457279779</v>
+        <v>1.676512340430893</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.92246213443286</v>
+        <v>-10.80938399584767</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.237427939271859</v>
+        <v>-1.192196683837782</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.752825852930005</v>
+        <v>-2.639747714344815</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.480217827057029</v>
+        <v>1.548064710208144</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.91877120947645</v>
+        <v>-10.80569307089126</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.235951569289295</v>
+        <v>-1.190720313855218</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.752825852930005</v>
+        <v>-2.639747714344815</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.480217827057029</v>
+        <v>1.548064710208144</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.12302938480631</v>
+        <v>-11.00995124622112</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.312141642302598</v>
+        <v>-1.266910386868521</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.880464797543994</v>
+        <v>-2.767386658958804</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.409147657407279</v>
+        <v>1.476994540558393</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.34106715643749</v>
+        <v>-11.2279890178523</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.394874196470633</v>
+        <v>-1.349642941036557</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.055235565639893</v>
+        <v>-2.942157427054703</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.308767751034175</v>
+        <v>1.37661463418529</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.26759732477004</v>
+        <v>-11.15451918618485</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.350114562310233</v>
+        <v>-1.304883306876156</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.981765733972445</v>
+        <v>-2.868687595387254</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.368221351528065</v>
+        <v>1.43606823467918</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.44272174215659</v>
+        <v>-11.32964360357139</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.405609108517333</v>
+        <v>-1.360377853083256</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.156890151358989</v>
+        <v>-3.043812012773798</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.277701921843656</v>
+        <v>1.34554880499477</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.67717383617108</v>
+        <v>-11.56409569758588</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.506609111024725</v>
+        <v>-1.461377855590648</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.156890151358989</v>
+        <v>-3.043812012773798</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.27048275694206</v>
+        <v>1.338329640093174</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.96497768070831</v>
+        <v>-11.85189954212312</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.628402839613596</v>
+        <v>-1.58317158417952</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.444693995896227</v>
+        <v>-3.331615857311036</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.091128259445741</v>
+        <v>1.158975142596855</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.19480212787214</v>
+        <v>-12.08172398928695</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.71921682864057</v>
+        <v>-1.673985573206494</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.607341532966387</v>
+        <v>-3.494263394381197</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9946555270422008</v>
+        <v>1.062502410193315</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.4268310476084</v>
+        <v>-12.31375290902321</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.80933466790596</v>
+        <v>-1.764103412471884</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.669354230154811</v>
+        <v>-3.55627609156962</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9601416373582614</v>
+        <v>1.027988520509376</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.37481553363959</v>
+        <v>-12.2617373950544</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.784538126632034</v>
+        <v>-1.739306871197957</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.669354230154811</v>
+        <v>-3.55627609156962</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9641319730446622</v>
+        <v>1.031978856195777</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.51648737536371</v>
+        <v>-12.40340923677852</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.842682090220424</v>
+        <v>-1.797450834786347</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.669354230154811</v>
+        <v>-3.55627609156962</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9626567461459206</v>
+        <v>1.030503629297035</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.46689653093887</v>
+        <v>-12.35381839235368</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.807792342285618</v>
+        <v>-1.762561086851541</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.619763385729977</v>
+        <v>-3.506685247144786</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.007464662965693</v>
+        <v>1.075311546116808</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.36941509139199</v>
+        <v>-12.27207652437104</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.781850900113548</v>
+        <v>-1.742915473305166</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.583522111358982</v>
+        <v>-3.497520020390723</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.016158293941607</v>
+        <v>1.067759548522563</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.14356993867258</v>
+        <v>-12.04623137165163</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.681933765989575</v>
+        <v>-1.642998339181193</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.541595435771819</v>
+        <v>-3.455593344803559</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.050893372330114</v>
+        <v>1.102494626911069</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.85729512634989</v>
+        <v>-11.75995655932893</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.566284696504438</v>
+        <v>-1.527349269696056</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.541595435771819</v>
+        <v>-3.455593344803559</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.052032516886173</v>
+        <v>1.103633771467128</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.91019041439417</v>
+        <v>-11.81285184737322</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.584809037560045</v>
+        <v>-1.545873610751663</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.536640089683373</v>
+        <v>-3.450637998715113</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.057639498701348</v>
+        <v>1.109240753282303</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.62628168346542</v>
+        <v>-11.52894311644447</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.465511840949909</v>
+        <v>-1.426576414141527</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.536640089683373</v>
+        <v>-3.450637998715113</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.063373202939985</v>
+        <v>1.11497445752094</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.51086075932733</v>
+        <v>-11.41352219230637</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.429080733688536</v>
+        <v>-1.390145306880154</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.421219165545277</v>
+        <v>-3.335217074577018</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.122888495028977</v>
+        <v>1.174489749609932</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.24702389212326</v>
+        <v>-11.1496853251023</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.333429468119815</v>
+        <v>-1.294494041311433</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.421219165545277</v>
+        <v>-3.335217074577018</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.113005013716069</v>
+        <v>1.164606268297025</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.97978209125486</v>
+        <v>-10.8824435242339</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.22836730827183</v>
+        <v>-1.189431881463448</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.421219165545277</v>
+        <v>-3.335217074577018</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.111170453216695</v>
+        <v>1.162771707797651</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.85647616277664</v>
+        <v>-10.75913759575569</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.179345251854004</v>
+        <v>-1.140409825045622</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.331801494417714</v>
+        <v>-3.245799403449455</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.164520740919772</v>
+        <v>1.216121995500728</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.83252262180068</v>
+        <v>-10.73518405477973</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.169095329318127</v>
+        <v>-1.130159902509745</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.307847953441756</v>
+        <v>-3.221845862473497</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.17956137165084</v>
+        <v>1.231162626231796</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.56846268347789</v>
+        <v>-10.47112411645693</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.07673167015076</v>
+        <v>-1.037796243342378</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.04378801511896</v>
+        <v>-2.957785924150701</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.324737018482766</v>
+        <v>1.376338273063722</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.861383059973049</v>
+        <v>-9.764044492952094</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7966868544091259</v>
+        <v>-0.757751427600744</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.04378801511896</v>
+        <v>-2.957785924150701</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.321949984822465</v>
+        <v>1.373551239403421</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.821198761606858</v>
+        <v>-9.723860194585903</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7802695111748084</v>
+        <v>-0.7413340843664264</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.003603716752769</v>
+        <v>-2.91760162578451</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.346404187730021</v>
+        <v>1.398005442310977</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.741128966069054</v>
+        <v>-9.643790399048099</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7488747717389295</v>
+        <v>-0.7099393449305476</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.923533921214965</v>
+        <v>-2.837531830246706</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.39381288627346</v>
+        <v>1.445414140854416</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.507647743839456</v>
+        <v>-9.410309176818501</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6475578540092384</v>
+        <v>-0.608622427200856</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.690052698985367</v>
+        <v>-2.604050608017107</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.541826048449072</v>
+        <v>1.593427303030028</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.327939213695583</v>
+        <v>-9.230600646674628</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.578566652264648</v>
+        <v>-0.5396312254562661</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.632881194822671</v>
+        <v>-2.546879103854411</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.57323674063373</v>
+        <v>1.624837995214686</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.195663740064695</v>
+        <v>-9.09832517304374</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.530288976065266</v>
+        <v>-0.4913535492568841</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.500605721191784</v>
+        <v>-2.414603630223525</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.647969511559289</v>
+        <v>1.699570766140245</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-9.005064065391542</v>
+        <v>-8.907725498370587</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4512340455083681</v>
+        <v>-0.4122986186999857</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.310006046518632</v>
+        <v>-2.224003955550372</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.765144377050818</v>
+        <v>1.816745631631773</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.756064266707961</v>
+        <v>-8.658725699687006</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3387277848112769</v>
+        <v>-0.2997923580028945</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.310006046518632</v>
+        <v>-2.224003955550372</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.778050718274476</v>
+        <v>1.829651972855432</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.861654256481065</v>
+        <v>-8.76431568946011</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5089397103197371</v>
+        <v>-0.4700042835113551</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.415596036291736</v>
+        <v>-2.329593945323477</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.586720794811395</v>
+        <v>1.63832204939235</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.880389158599662</v>
+        <v>-8.783050591578707</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4678893292900899</v>
+        <v>-0.4289539024817075</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.415596036291736</v>
+        <v>-2.348328847442074</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.635265136688481</v>
+        <v>1.675625449998279</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.732449117192063</v>
+        <v>-8.635110550171108</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5285922354152177</v>
+        <v>-0.4896568086068354</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.395275120383178</v>
+        <v>-2.328007931533516</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.527578763545448</v>
+        <v>1.567939076855246</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.708220480803091</v>
+        <v>-8.610881913782135</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5276147671131066</v>
+        <v>-0.4886793403047247</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.371046483994206</v>
+        <v>-2.303779295144544</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.533401959125353</v>
+        <v>1.573762272435151</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.664672074032399</v>
+        <v>-8.567333507011444</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5171560164999232</v>
+        <v>-0.4782205896915412</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.371046483994206</v>
+        <v>-2.303779295144544</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.52644134703026</v>
+        <v>1.566801660340058</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.422523680578541</v>
+        <v>-8.325185113557586</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.4058343047372368</v>
+        <v>-0.3668988779288549</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.371046483994206</v>
+        <v>-2.303779295144544</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.540903701411403</v>
+        <v>1.581264014721201</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.359294308810194</v>
+        <v>-8.261955741789238</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3860104355707028</v>
+        <v>-0.3470750087623209</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.371046483994206</v>
+        <v>-2.303779295144544</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.535435821870598</v>
+        <v>1.575796135180396</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.236003173993064</v>
+        <v>-8.138664606972108</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3391958876332741</v>
+        <v>-0.3002604608248922</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.247755349177076</v>
+        <v>-2.180488160327414</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.606908596771454</v>
+        <v>1.647268910081251</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.214853975089621</v>
+        <v>-8.117515408068666</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3230352298345718</v>
+        <v>-0.2840998030261899</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.226606150273633</v>
+        <v>-2.15933896142397</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.627299094350845</v>
+        <v>1.667659407660642</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788092</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.971088533106177</v>
+        <v>-7.873749966085222</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2297483446941437</v>
+        <v>-0.1908129178857614</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.226606150273633</v>
+        <v>-2.15933896142397</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.623079802697895</v>
+        <v>1.663440116007693</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.707060465912917</v>
+        <v>-7.609721898891962</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1220128038968236</v>
+        <v>-0.08307737708844165</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.024740751457679</v>
+        <v>-1.957473562608017</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.746323355907483</v>
+        <v>1.786683669217281</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.457210071963843</v>
+        <v>-7.359871504942888</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.02933057133349193</v>
+        <v>0.009604855474890428</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.024740751457679</v>
+        <v>-1.957473562608017</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.739065430891185</v>
+        <v>1.779425744200983</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.153642582959864</v>
+        <v>-7.056304015938909</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.09569554778874867</v>
+        <v>0.1346309745971306</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.024740751457679</v>
+        <v>-1.957473562608017</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.742664554411834</v>
+        <v>1.783024867721632</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.08016267410785</v>
+        <v>-6.982824107086895</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1384150173841077</v>
+        <v>0.17735044419249</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.951260842605665</v>
+        <v>-1.883993653756002</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.800080005777597</v>
+        <v>1.840440319087394</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.855129674439027</v>
+        <v>-6.757791107418072</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2274486948679337</v>
+        <v>0.2663841216763161</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.726227842936842</v>
+        <v>-1.65896065408718</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.934120283195187</v>
+        <v>1.974480596504985</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.64049529680262</v>
+        <v>-6.543156729781665</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3179972469768138</v>
+        <v>0.3569326737851961</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.511593465300435</v>
+        <v>-1.444326276450773</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.067595710831349</v>
+        <v>2.107956024141146</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.373894939828268</v>
+        <v>-6.276556372807313</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4058316485503504</v>
+        <v>0.4447670753587323</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.511593465300435</v>
+        <v>-1.444326276450773</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.048789969615144</v>
+        <v>2.089150282924942</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712292</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.133464443023408</v>
+        <v>-6.036125876002453</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5037469238971717</v>
+        <v>0.542682350705554</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.271162968495575</v>
+        <v>-1.203895779645912</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.194791344322938</v>
+        <v>2.235151657632735</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.890673635373963</v>
+        <v>-5.793335068353008</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6047925607917701</v>
+        <v>0.6437279876001525</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.271162968495575</v>
+        <v>-1.203895779645912</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.198720658157758</v>
+        <v>2.239080971467556</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.774733785748777</v>
+        <v>-5.677395218727822</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6518470845591842</v>
+        <v>0.6907825113675665</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.194341237479451</v>
+        <v>-1.127074048629789</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.245492280684772</v>
+        <v>2.28585259399457</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.532078197325614</v>
+        <v>-5.434739630304659</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7459073911484433</v>
+        <v>0.7848428179568252</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.194341237479451</v>
+        <v>-1.127074048629789</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.242490351904766</v>
+        <v>2.282850665214563</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145936</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.312057399288603</v>
+        <v>-5.214718832267648</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8354947473738616</v>
+        <v>0.8744301741822436</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.053121392411471</v>
+        <v>-0.9858542035618083</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.328801295956168</v>
+        <v>2.369161609265966</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009948</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.112808769383794</v>
+        <v>-5.015470202362839</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9310883821376086</v>
+        <v>0.9700238089459905</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.053121392411471</v>
+        <v>-0.9858542035618083</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.344695478757991</v>
+        <v>2.385055792067789</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.953293665864424</v>
+        <v>-4.855955098843469</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9960402679856584</v>
+        <v>1.034975694794041</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8936062888921007</v>
+        <v>-0.8263391000424384</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.441550385309915</v>
+        <v>2.481910698619713</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.808621520764687</v>
+        <v>-4.711282953743732</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.063997228586993</v>
+        <v>1.102932655395375</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7489341437923633</v>
+        <v>-0.681666954942701</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.538441774931198</v>
+        <v>2.578802088240995</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412101</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.868496348122379</v>
+        <v>-4.771157781101424</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.026084789045342</v>
+        <v>1.065020215853724</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.8088089711500555</v>
+        <v>-0.7415417823003931</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.488554369918008</v>
+        <v>2.528914683227805</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.781696850343371</v>
+        <v>-4.684358283322416</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.083205081479512</v>
+        <v>1.122140508287894</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.8088089711500555</v>
+        <v>-0.7415417823003931</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.510954863240574</v>
+        <v>2.551315176550371</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.784166556805177</v>
+        <v>-4.686827989784222</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.082289600268201</v>
+        <v>1.121225027076583</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.8112786776118617</v>
+        <v>-0.7440114887621994</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.509545440736903</v>
+        <v>2.5499057540467</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.989623696939967</v>
+        <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.852536743129187</v>
+        <v>-4.755198176108232</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.048252575374545</v>
+        <v>1.104883875021681</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.8020029785756467</v>
+        <v>-0.7347357897259844</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.508421909794579</v>
+        <v>2.566478095943131</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.980060405571859</v>
+        <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.731120313502711</v>
+        <v>-4.633781746481755</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.087255855857027</v>
+        <v>1.143887155504163</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.8020029785756467</v>
+        <v>-0.7347357897259844</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.498858618426471</v>
+        <v>2.556914804575023</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.804769970612246</v>
+        <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.762113472831416</v>
+        <v>-4.664774905810461</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8995681571659317</v>
+        <v>0.9561994568130678</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.8020029785756467</v>
+        <v>-0.7347357897259844</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.323568183466858</v>
+        <v>2.381624369615409</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.809337202604033</v>
+        <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.586639213038946</v>
+        <v>-4.489300646017991</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9743250930747074</v>
+        <v>1.030956392721843</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.8020029785756467</v>
+        <v>-0.7347357897259844</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.328135415458646</v>
+        <v>2.386191601607197</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695447</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.809348676490831</v>
+        <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.697575465680195</v>
+        <v>-4.60023689865924</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9299620659050054</v>
+        <v>0.9865933655521415</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.8020029785756467</v>
+        <v>-0.7347357897259844</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.328146889345443</v>
+        <v>2.386203075493994</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.812480061710736</v>
+        <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.900602043223429</v>
+        <v>-4.803263476202473</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8518828201076176</v>
+        <v>0.9085141197547537</v>
       </c>
       <c r="F1941" t="n">
-        <v>-1.00502955611888</v>
+        <v>-0.9377623672692178</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.209462328039408</v>
+        <v>2.26751851418796</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434037673416</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.822652448142869</v>
+        <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.742676444288136</v>
+        <v>-4.64533787726718</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9252254461138674</v>
+        <v>0.9818567457610032</v>
       </c>
       <c r="F1942" t="n">
-        <v>-1.00502955611888</v>
+        <v>-0.9377623672692178</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.219634714471541</v>
+        <v>2.277690900620092</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212296</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.817598718716729</v>
+        <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.890997698099264</v>
+        <v>-4.793659131078309</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8608432151632761</v>
+        <v>0.9174745148104122</v>
       </c>
       <c r="F1943" t="n">
-        <v>-1.00502955611888</v>
+        <v>-0.9377623672692178</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.214580985045401</v>
+        <v>2.272637171193953</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.809374494161255</v>
+        <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.892180782750325</v>
+        <v>-4.79484221572937</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8521457567473774</v>
+        <v>0.9087770563945134</v>
       </c>
       <c r="F1944" t="n">
-        <v>-1.010672604585392</v>
+        <v>-0.9434054157357293</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.20297093141002</v>
+        <v>2.261027117558571</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.809926367194356</v>
+        <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.769053075756242</v>
+        <v>-4.671714508735286</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9019487125781123</v>
+        <v>0.9585800122252484</v>
       </c>
       <c r="F1945" t="n">
-        <v>-1.010672604585392</v>
+        <v>-0.9434054157357293</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.203522804443121</v>
+        <v>2.261578990591673</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.739199059085722</v>
+        <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.676242594305382</v>
+        <v>-4.578904027284427</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8683455970498217</v>
+        <v>0.9249768966969578</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.9178621231345324</v>
+        <v>-0.85059493428487</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.188481785205003</v>
+        <v>2.246537971353554</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.741072535010323</v>
+        <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.627679542084352</v>
+        <v>-4.530340975063397</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8896442938628346</v>
+        <v>0.9462755935099705</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8692990709135022</v>
+        <v>-0.8020318820638398</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.219493092462222</v>
+        <v>2.277549278610773</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.736148243522046</v>
+        <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.515008323848102</v>
+        <v>-4.417669756827147</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9297884896690576</v>
+        <v>0.9864197893161937</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.756627852677252</v>
+        <v>-0.6893606638275895</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.282171531915695</v>
+        <v>2.340227718064246</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.741639539352713</v>
+        <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.402631322665429</v>
+        <v>-4.305292755644474</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.980230585972794</v>
+        <v>1.03686188561993</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.756627852677252</v>
+        <v>-0.6893606638275895</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.287662827746362</v>
+        <v>2.345719013894914</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.753136741121252</v>
+        <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.621094093151122</v>
+        <v>-4.503527324531205</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9043426795470559</v>
+        <v>0.9690652598337768</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.975090623162945</v>
+        <v>-0.8875952327143202</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.168082367223485</v>
+        <v>2.238275474331414</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.379769649168515</v>
+        <v>3.741828918809899</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.647346843331023</v>
+        <v>2.773925668739768</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.621094093151122</v>
+        <v>-4.629246814975953</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9043426795470559</v>
+        <v>0.9218705184356399</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.975090623162945</v>
+        <v>-0.9340298416977387</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.640410640317391</v>
+        <v>2.213507763721125</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240501.xlsx
+++ b/tame_output/ON/bt/strategyON_20240501.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>56.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.0%</t>
+          <t>-81.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>138.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-706.3%</t>
+          <t>-720.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.2%</t>
+          <t>-56.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.6%</t>
+          <t>444.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-624.5%</t>
+          <t>-627.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-282.9%</t>
+          <t>-288.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.4%</t>
+          <t>-42.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-63.9%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-284.0%</t>
+          <t>-285.2%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.9%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-330.5%</t>
+          <t>-344.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.9%</t>
+          <t>-160.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-317.4%</t>
+          <t>-314.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-198.7%</t>
+          <t>-207.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-224.7%</t>
+          <t>-222.7%</t>
         </is>
       </c>
     </row>
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.070845918412017</v>
+        <v>-2.214663751145058</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.28130977506976</v>
+        <v>2.223782641976543</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4560904921569849</v>
+        <v>0.312272659423944</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.383658862042505</v>
+        <v>3.29736816240268</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.398863140139496</v>
+        <v>-2.542680972872537</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.170441176117536</v>
+        <v>2.11291404302432</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1280732704295057</v>
+        <v>-0.01574456230353516</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.207186818744785</v>
+        <v>3.120896119104961</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.892188011674674</v>
+        <v>-3.036005844407715</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.981209977912034</v>
+        <v>1.923682844818817</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.02308715618988699</v>
+        <v>-0.1207306765431539</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.152293900609583</v>
+        <v>3.066003200969758</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.384573039698771</v>
+        <v>-3.528390872431812</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.785362358746127</v>
+        <v>1.727835225652911</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4692978718342097</v>
+        <v>-0.6131157045672506</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.857969275838857</v>
+        <v>2.771678576199033</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.769753430628843</v>
+        <v>-3.913571263361884</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.629832741186961</v>
+        <v>1.572305608093745</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4692978718342097</v>
+        <v>-0.6131157045672506</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.856511814651721</v>
+        <v>2.770221115011896</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.113436203855506</v>
+        <v>-4.257254036588547</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.494128755350912</v>
+        <v>1.436601622257696</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5772039238614279</v>
+        <v>-0.7210217565944688</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.793537306890006</v>
+        <v>2.707246607250181</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.471086554093854</v>
+        <v>-4.614904386826895</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.347174673911831</v>
+        <v>1.289647540818615</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.9348542740997761</v>
+        <v>-1.078672106832817</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.575053155403254</v>
+        <v>2.48876245576343</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.780320657089905</v>
+        <v>-4.924138489822946</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.22525395941367</v>
+        <v>1.167726826320454</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.9348542740997761</v>
+        <v>-1.078672106832817</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.576826082103514</v>
+        <v>2.49053538246369</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.212126450239692</v>
+        <v>-5.355944282972733</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.03886452962116</v>
+        <v>0.9813373965279433</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.071271770541043</v>
+        <v>-1.215089603274084</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.481308471706158</v>
+        <v>2.395017772066334</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.446820444372245</v>
+        <v>-5.590638277105286</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9332717069702294</v>
+        <v>0.8757445738770131</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.064935503311788</v>
+        <v>-1.208753336044829</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.473395007045802</v>
+        <v>2.387104307405978</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.782483091602697</v>
+        <v>-5.926300924335738</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7975872397340136</v>
+        <v>0.7400601066407972</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.064935503311788</v>
+        <v>-1.208753336044829</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.471975598701767</v>
+        <v>2.385684899061943</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.14610933650301</v>
+        <v>-6.289927169236051</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6586243020081297</v>
+        <v>0.6010971689149134</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.163157140178914</v>
+        <v>-1.306974972911954</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.419530176815733</v>
+        <v>2.333239477175909</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.511236719141757</v>
+        <v>-6.655054551874798</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5118278639584624</v>
+        <v>0.454300730865246</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.459467924477926</v>
+        <v>-1.603285757210967</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.240998221242157</v>
+        <v>2.154707521602333</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.919825496322435</v>
+        <v>-7.063643329055477</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3471538971009505</v>
+        <v>0.2896267640077337</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.868056701658605</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.994606498948509</v>
+        <v>1.908315799308685</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.332807980463529</v>
+        <v>-7.476625813196571</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1771463359159733</v>
+        <v>0.1196192028227565</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.868056701658605</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.98979193141997</v>
+        <v>1.903501231780145</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.749199854750526</v>
+        <v>-7.893017687483568</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.008583636810051587</v>
+        <v>-0.04894349628316519</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.868056701658605</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.987785982028847</v>
+        <v>1.901495282389023</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.12587686528037</v>
+        <v>-8.269694698013412</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1318284767332067</v>
+        <v>-0.1893556098264235</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.868056701658605</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.998044672697526</v>
+        <v>1.911753973057702</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.471751687265179</v>
+        <v>-8.615569519998221</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2740788403814354</v>
+        <v>-0.3316059734746521</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.868056701658605</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.994144237843221</v>
+        <v>1.907853538203397</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.633893957728272</v>
+        <v>-8.777711790461314</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3405308285116715</v>
+        <v>-0.3980579616048883</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.868056701658605</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.992549157898222</v>
+        <v>1.906258458258398</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.93055529953847</v>
+        <v>-9.074373132271512</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4554163893065426</v>
+        <v>-0.5129435223997594</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.936799837392483</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.955082252387103</v>
+        <v>1.868791552747279</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.363904407648706</v>
+        <v>-9.507722240381748</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6327823370850396</v>
+        <v>-0.6903094701782564</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.936799837392483</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.9510559478527</v>
+        <v>1.864765248212876</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.746905796391337</v>
+        <v>-9.890723629124379</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7860849939036765</v>
+        <v>-0.8436121269968933</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.936799837392483</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.950953846531116</v>
+        <v>1.864663146891292</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.904304676604458</v>
+        <v>-10.0481225093375</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8464730300174943</v>
+        <v>-0.9040001631107111</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.094198717605604</v>
+        <v>-2.238016550338645</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.859086034374674</v>
+        <v>1.772795334734849</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.26383499910846</v>
+        <v>-10.4076528318415</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9849348557210451</v>
+        <v>-1.042461988814262</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.094198717605604</v>
+        <v>-2.238016550338645</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.864436337672724</v>
+        <v>1.778145638032899</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.59023502777347</v>
+        <v>-10.73405286050651</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.107578847229873</v>
+        <v>-1.165105980323089</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.420598746270617</v>
+        <v>-2.564416579003658</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.676512340430893</v>
+        <v>1.590221640791069</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.80938399584767</v>
+        <v>-10.95320182858071</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.192196683837782</v>
+        <v>-1.249723816930999</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.639747714344815</v>
+        <v>-2.783565547077855</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.548064710208144</v>
+        <v>1.461774010568319</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.80569307089126</v>
+        <v>-10.9495109036243</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.190720313855218</v>
+        <v>-1.248247446948435</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.639747714344815</v>
+        <v>-2.783565547077855</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.548064710208144</v>
+        <v>1.461774010568319</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.00995124622112</v>
+        <v>-11.15376907895416</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.266910386868521</v>
+        <v>-1.324437519961738</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.767386658958804</v>
+        <v>-2.911204491691844</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.476994540558393</v>
+        <v>1.390703840918569</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.2279890178523</v>
+        <v>-11.37180685058534</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.349642941036557</v>
+        <v>-1.407170074129774</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.942157427054703</v>
+        <v>-3.085975259787743</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.37661463418529</v>
+        <v>1.290323934545465</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.15451918618485</v>
+        <v>-11.29833701891789</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.304883306876156</v>
+        <v>-1.362410439969373</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.868687595387254</v>
+        <v>-3.012505428120295</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.43606823467918</v>
+        <v>1.349777535039355</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.32964360357139</v>
+        <v>-11.47346143630444</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.360377853083256</v>
+        <v>-1.417904986176473</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.043812012773798</v>
+        <v>-3.187629845506839</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.34554880499477</v>
+        <v>1.259258105354946</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.56409569758588</v>
+        <v>-11.70791353031893</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.461377855590648</v>
+        <v>-1.518904988683865</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.043812012773798</v>
+        <v>-3.187629845506839</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.338329640093174</v>
+        <v>1.25203894045335</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.85189954212312</v>
+        <v>-11.99571737485616</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.58317158417952</v>
+        <v>-1.640698717272736</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.331615857311036</v>
+        <v>-3.475433690044077</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.158975142596855</v>
+        <v>1.072684442957031</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.08172398928695</v>
+        <v>-12.22554182201999</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.673985573206494</v>
+        <v>-1.731512706299711</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.494263394381197</v>
+        <v>-3.638081227114237</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.062502410193315</v>
+        <v>0.9762117105534909</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.31375290902321</v>
+        <v>-12.45757074175625</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.764103412471884</v>
+        <v>-1.821630545565101</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.55627609156962</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.027988520509376</v>
+        <v>0.9416978208695514</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.2617373950544</v>
+        <v>-12.40555522778744</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.739306871197957</v>
+        <v>-1.796834004291174</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.55627609156962</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.031978856195777</v>
+        <v>0.9456881565559523</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.40340923677852</v>
+        <v>-12.54722706951156</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.797450834786347</v>
+        <v>-1.854977967879564</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.55627609156962</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.030503629297035</v>
+        <v>0.9442129296572106</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.35381839235368</v>
+        <v>-12.49763622508672</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.762561086851541</v>
+        <v>-1.820088219944758</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.506685247144786</v>
+        <v>-3.650503079877827</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.075311546116808</v>
+        <v>0.9890208464769832</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.27207652437104</v>
+        <v>-12.29848411784963</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.742915473305166</v>
+        <v>-1.753478510696601</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.497520020390723</v>
+        <v>-3.485180553928013</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.067759548522563</v>
+        <v>1.075163228400188</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.04623137165163</v>
+        <v>-12.07263896513021</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.642998339181193</v>
+        <v>-1.653561376572628</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.455593344803559</v>
+        <v>-3.44325387834085</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.102494626911069</v>
+        <v>1.109898306788695</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.75995655932893</v>
+        <v>-11.78636415280752</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.527349269696056</v>
+        <v>-1.537912307087491</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.455593344803559</v>
+        <v>-3.44325387834085</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.103633771467128</v>
+        <v>1.111037451344754</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.81285184737322</v>
+        <v>-11.83925944085181</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.545873610751663</v>
+        <v>-1.556436648143098</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.450637998715113</v>
+        <v>-3.438298532252404</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.109240753282303</v>
+        <v>1.116644433159929</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.52894311644447</v>
+        <v>-11.55535070992306</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.426576414141527</v>
+        <v>-1.437139451532962</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.450637998715113</v>
+        <v>-3.438298532252404</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.11497445752094</v>
+        <v>1.122378137398566</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.41352219230637</v>
+        <v>-11.43992978578496</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.390145306880154</v>
+        <v>-1.400708344271589</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.335217074577018</v>
+        <v>-3.322877608114308</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.174489749609932</v>
+        <v>1.181893429487558</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.1496853251023</v>
+        <v>-11.17609291858089</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.294494041311433</v>
+        <v>-1.305057078702868</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.335217074577018</v>
+        <v>-3.322877608114308</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.164606268297025</v>
+        <v>1.17200994817465</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.8824435242339</v>
+        <v>-10.90885111771249</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.189431881463448</v>
+        <v>-1.199994918854884</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.335217074577018</v>
+        <v>-3.322877608114308</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.162771707797651</v>
+        <v>1.170175387675277</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.75913759575569</v>
+        <v>-10.78554518923427</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.140409825045622</v>
+        <v>-1.150972862437057</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.245799403449455</v>
+        <v>-3.233459936986745</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.216121995500728</v>
+        <v>1.223525675378353</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.73518405477973</v>
+        <v>-10.76159164825832</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.130159902509745</v>
+        <v>-1.14072293990118</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.221845862473497</v>
+        <v>-3.209506396010788</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.231162626231796</v>
+        <v>1.238566306109422</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.47112411645693</v>
+        <v>-10.49753170993552</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.037796243342378</v>
+        <v>-1.048359280733813</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.957785924150701</v>
+        <v>-2.945446457687992</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.376338273063722</v>
+        <v>1.383741952941347</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.764044492952094</v>
+        <v>-9.790452086430681</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.757751427600744</v>
+        <v>-0.7683144649921791</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.957785924150701</v>
+        <v>-2.945446457687992</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.373551239403421</v>
+        <v>1.380954919281046</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.723860194585903</v>
+        <v>-9.750267788064491</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7413340843664264</v>
+        <v>-0.7518971217578616</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.91760162578451</v>
+        <v>-2.905262159321801</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.398005442310977</v>
+        <v>1.405409122188602</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.643790399048099</v>
+        <v>-9.670197992526687</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7099393449305476</v>
+        <v>-0.7205023823219827</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.837531830246706</v>
+        <v>-2.825192363783997</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.445414140854416</v>
+        <v>1.452817820732042</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.410309176818501</v>
+        <v>-9.436716770297089</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.608622427200856</v>
+        <v>-0.6191854645922912</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.604050608017107</v>
+        <v>-2.591711141554398</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.593427303030028</v>
+        <v>1.600830982907653</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.230600646674628</v>
+        <v>-9.257008240153215</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5396312254562661</v>
+        <v>-0.5501942628477012</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.546879103854411</v>
+        <v>-2.534539637391702</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.624837995214686</v>
+        <v>1.632241675092311</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.09832517304374</v>
+        <v>-9.124732766522328</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4913535492568841</v>
+        <v>-0.5019165866483193</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.414603630223525</v>
+        <v>-2.402264163760816</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.699570766140245</v>
+        <v>1.70697444601787</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.907725498370587</v>
+        <v>-8.934133091849175</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4122986186999857</v>
+        <v>-0.4228616560914209</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.224003955550372</v>
+        <v>-2.211664489087663</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.816745631631773</v>
+        <v>1.824149311509399</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.658725699687006</v>
+        <v>-8.685133293165594</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2997923580028945</v>
+        <v>-0.3103553953943297</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.224003955550372</v>
+        <v>-2.211664489087663</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.829651972855432</v>
+        <v>1.837055652733057</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.76431568946011</v>
+        <v>-8.790723282938698</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4700042835113551</v>
+        <v>-0.4805673209027903</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.329593945323477</v>
+        <v>-2.317254478860768</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.63832204939235</v>
+        <v>1.645725729269976</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.783050591578707</v>
+        <v>-8.637909207550246</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4289539024817075</v>
+        <v>-0.3708973488703231</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.348328847442074</v>
+        <v>-2.164440403472316</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.675625449998279</v>
+        <v>1.785958516380133</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.635110550171108</v>
+        <v>-8.489969166142647</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4896568086068354</v>
+        <v>-0.431600254995451</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.328007931533516</v>
+        <v>-2.144119487563759</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.567939076855246</v>
+        <v>1.6782721432371</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.610881913782135</v>
+        <v>-8.465740529753674</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4886793403047247</v>
+        <v>-0.4306227866933403</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.303779295144544</v>
+        <v>-2.119890851174786</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.573762272435151</v>
+        <v>1.684095338817005</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568104</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.567333507011444</v>
+        <v>-8.422192122982983</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4782205896915412</v>
+        <v>-0.4201640360801568</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.303779295144544</v>
+        <v>-2.119890851174786</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.566801660340058</v>
+        <v>1.677134726721912</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963415</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.325185113557586</v>
+        <v>-8.180043729529125</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3668988779288549</v>
+        <v>-0.3088423243174705</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.303779295144544</v>
+        <v>-2.119890851174786</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.581264014721201</v>
+        <v>1.691597081103055</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.261955741789238</v>
+        <v>-8.116814357760777</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3470750087623209</v>
+        <v>-0.2890184551509365</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.303779295144544</v>
+        <v>-2.119890851174786</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.575796135180396</v>
+        <v>1.68612920156225</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.138664606972108</v>
+        <v>-7.993523222943646</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3002604608248922</v>
+        <v>-0.2422039072135074</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.180488160327414</v>
+        <v>-1.996599716357656</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.647268910081251</v>
+        <v>1.757601976463105</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.117515408068666</v>
+        <v>-7.972374024040203</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2840998030261899</v>
+        <v>-0.2260432494148046</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.15933896142397</v>
+        <v>-1.975450517454213</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.667659407660642</v>
+        <v>1.777992474042497</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.74832483278809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.873749966085222</v>
+        <v>-7.728608582056759</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1908129178857614</v>
+        <v>-0.1327563642743761</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.15933896142397</v>
+        <v>-1.975450517454213</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.663440116007693</v>
+        <v>1.773773182389547</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.609721898891962</v>
+        <v>-7.464580514863499</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.08307737708844165</v>
+        <v>-0.02502082347705636</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.957473562608017</v>
+        <v>-1.773585118638259</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.786683669217281</v>
+        <v>1.897016735599135</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.359871504942888</v>
+        <v>-7.214730120914425</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.009604855474890428</v>
+        <v>0.06766140908627571</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.957473562608017</v>
+        <v>-1.773585118638259</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.779425744200983</v>
+        <v>1.889758810582838</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.056304015938909</v>
+        <v>-6.911162631910446</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1346309745971306</v>
+        <v>0.1926875282085159</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.957473562608017</v>
+        <v>-1.773585118638259</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.783024867721632</v>
+        <v>1.893357934103486</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.982824107086895</v>
+        <v>-6.837682723058432</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.17735044419249</v>
+        <v>0.2354069978038749</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.883993653756002</v>
+        <v>-1.700105209786245</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.840440319087394</v>
+        <v>1.950773385469248</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.757791107418072</v>
+        <v>-6.612649723389609</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2663841216763161</v>
+        <v>0.3244406752877014</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.65896065408718</v>
+        <v>-1.475072210117422</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.974480596504985</v>
+        <v>2.084813662886839</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.543156729781665</v>
+        <v>-6.398015345753202</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3569326737851961</v>
+        <v>0.4149892273965814</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.444326276450773</v>
+        <v>-1.260437832481015</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.107956024141146</v>
+        <v>2.218289090523001</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.276556372807313</v>
+        <v>-6.13141498877885</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4447670753587323</v>
+        <v>0.5028236289701176</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.444326276450773</v>
+        <v>-1.260437832481015</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.089150282924942</v>
+        <v>2.199483349306796</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.036125876002453</v>
+        <v>-5.89098449197399</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.542682350705554</v>
+        <v>0.6007389043169393</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.203895779645912</v>
+        <v>-1.020007335676155</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.235151657632735</v>
+        <v>2.34548472401459</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.793335068353008</v>
+        <v>-5.648193684324545</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6437279876001525</v>
+        <v>0.7017845412115373</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.203895779645912</v>
+        <v>-1.020007335676155</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.239080971467556</v>
+        <v>2.34941403784941</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.677395218727822</v>
+        <v>-5.532253834699359</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6907825113675665</v>
+        <v>0.7488390649789518</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.127074048629789</v>
+        <v>-0.9431856046600311</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.28585259399457</v>
+        <v>2.396185660376424</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.434739630304659</v>
+        <v>-5.289598246276196</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7848428179568252</v>
+        <v>0.8428993715682105</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.127074048629789</v>
+        <v>-0.9431856046600311</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.282850665214563</v>
+        <v>2.393183731596418</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.214718832267648</v>
+        <v>-5.069577448239185</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8744301741822436</v>
+        <v>0.9324867277936288</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9858542035618083</v>
+        <v>-0.8019657595920509</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.369161609265966</v>
+        <v>2.47949467564782</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.015470202362839</v>
+        <v>-4.870328818334376</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9700238089459905</v>
+        <v>1.028080362557376</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9858542035618083</v>
+        <v>-0.8019657595920509</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.385055792067789</v>
+        <v>2.495388858449643</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.855955098843469</v>
+        <v>-4.710813714815006</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.034975694794041</v>
+        <v>1.093032248405426</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8263391000424384</v>
+        <v>-0.6424506560726809</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.481910698619713</v>
+        <v>2.592243765001567</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.711282953743732</v>
+        <v>-4.566141569715269</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.102932655395375</v>
+        <v>1.160989209006761</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.681666954942701</v>
+        <v>-0.4977785109729435</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.578802088240995</v>
+        <v>2.689135154622849</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.771157781101424</v>
+        <v>-4.626016397072961</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.065020215853724</v>
+        <v>1.123076769465109</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7415417823003931</v>
+        <v>-0.5576533383306357</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.528914683227805</v>
+        <v>2.63924774960966</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.684358283322416</v>
+        <v>-4.539216899293953</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.122140508287894</v>
+        <v>1.180197061899279</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7415417823003931</v>
+        <v>-0.5576533383306357</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.551315176550371</v>
+        <v>2.661648242932226</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.686827989784222</v>
+        <v>-4.541686605755759</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.121225027076583</v>
+        <v>1.179281580687969</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.7440114887621994</v>
+        <v>-0.5601230447924419</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.5499057540467</v>
+        <v>2.660238820428555</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.755198176108232</v>
+        <v>-4.610056792079769</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.104883875021681</v>
+        <v>1.162940428633066</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.7347357897259844</v>
+        <v>-0.550847345756227</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.566478095943131</v>
+        <v>2.676811162324985</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.633781746481755</v>
+        <v>-4.488640362453292</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.143887155504163</v>
+        <v>1.201943709115548</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.7347357897259844</v>
+        <v>-0.550847345756227</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.556914804575023</v>
+        <v>2.667247870956877</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.664774905810461</v>
+        <v>-4.519633521781998</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9561994568130678</v>
+        <v>1.014256010424453</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.7347357897259844</v>
+        <v>-0.550847345756227</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.381624369615409</v>
+        <v>2.491957435997263</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.489300646017991</v>
+        <v>-4.344159261989528</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.030956392721843</v>
+        <v>1.089012946333229</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.7347357897259844</v>
+        <v>-0.550847345756227</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.386191601607197</v>
+        <v>2.496524667989052</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695447</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.60023689865924</v>
+        <v>-4.455095514630777</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9865933655521415</v>
+        <v>1.044649919163527</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.7347357897259844</v>
+        <v>-0.550847345756227</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.386203075493994</v>
+        <v>2.496536141875849</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.803263476202473</v>
+        <v>-4.65812209217401</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9085141197547537</v>
+        <v>0.966570673366139</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.9377623672692178</v>
+        <v>-0.7538739232994603</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.26751851418796</v>
+        <v>2.377851580569815</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.784340376734158</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.64533787726718</v>
+        <v>-4.500196493238717</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9818567457610032</v>
+        <v>1.039913299372389</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.9377623672692178</v>
+        <v>-0.7538739232994603</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.277690900620092</v>
+        <v>2.388023967001947</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212294</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.793659131078309</v>
+        <v>-4.648517747049846</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9174745148104122</v>
+        <v>0.9755310684217973</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.9377623672692178</v>
+        <v>-0.7538739232994603</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.272637171193953</v>
+        <v>2.382970237575807</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786042</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.79484221572937</v>
+        <v>-4.649700831700907</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9087770563945134</v>
+        <v>0.9668336100058987</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.9434054157357293</v>
+        <v>-0.7595169717659719</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.261027117558571</v>
+        <v>2.371360183940426</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.671714508735286</v>
+        <v>-4.526573124706823</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9585800122252484</v>
+        <v>1.016636565836633</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.9434054157357293</v>
+        <v>-0.7595169717659719</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.261578990591673</v>
+        <v>2.371912056973527</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.578904027284427</v>
+        <v>-4.433762643255964</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9249768966969578</v>
+        <v>0.9830334503083429</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.85059493428487</v>
+        <v>-0.6667064903151125</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.246537971353554</v>
+        <v>2.356871037735409</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.530340975063397</v>
+        <v>-4.385199591034934</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9462755935099705</v>
+        <v>1.004332147121356</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8020318820638398</v>
+        <v>-0.6181434380940823</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.277549278610773</v>
+        <v>2.387882344992628</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.417669756827147</v>
+        <v>-4.272528372798684</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9864197893161937</v>
+        <v>1.044476342927579</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.6893606638275895</v>
+        <v>-0.5054722198578321</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.340227718064246</v>
+        <v>2.4505607844461</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.305292755644474</v>
+        <v>-4.160151371616011</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.03686188561993</v>
+        <v>1.094918439231315</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.6893606638275895</v>
+        <v>-0.5054722198578321</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.345719013894914</v>
+        <v>2.456052080276768</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968859</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.503527324531205</v>
+        <v>-4.455269965541116</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9690652598337768</v>
+        <v>0.9883682034298122</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.8875952327143202</v>
+        <v>-0.8005908137829369</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.238275474331414</v>
+        <v>2.290478125690244</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.741828918809899</v>
+        <v>3.844561348271624</v>
       </c>
       <c r="C1951" t="n">
         <v>2.773925668739768</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.629246814975953</v>
+        <v>-4.658657844908004</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9218705184356399</v>
+        <v>0.9101061064628193</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.9340298416977387</v>
+        <v>-0.900660492693635</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.213507763721125</v>
+        <v>2.233529373123587</v>
       </c>
     </row>
   </sheetData>
